--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vital Signs: SpO2</t>
+    <t>Vital Signs SpO2</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vital Signs SpO2</t>
+    <t>Vital Signs: SpO2</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -1807,16 +1807,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>1239: transform using Split_SpO2_value.Flow on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.SupplementalO2</t>
+  </si>
+  <si>
     <t>SN.2  / CQ - N/A</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>1239: transform using Split_SpO2_value.Flow on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.SupplementalO2</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.value[x].comparator</t>
@@ -2360,14 +2360,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="132.76171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="132.76171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2606,22 +2606,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3243,13 +3243,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3369,13 +3369,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3495,13 +3495,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3623,13 +3623,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3740,25 +3740,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3866,22 +3866,22 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3992,22 +3992,22 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4118,25 +4118,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -4253,16 +4253,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4383,16 +4383,16 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4507,13 +4507,13 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4633,13 +4633,13 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4758,16 +4758,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4885,13 +4885,13 @@
         <v>84</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -5011,13 +5011,13 @@
         <v>84</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5136,16 +5136,16 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
@@ -5262,16 +5262,16 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -5388,16 +5388,16 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5514,16 +5514,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5642,16 +5642,16 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5770,16 +5770,16 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5892,28 +5892,28 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AR28" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -6025,13 +6025,13 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -6151,13 +6151,13 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -6274,16 +6274,16 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6404,16 +6404,16 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6534,16 +6534,16 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6662,16 +6662,16 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6784,25 +6784,25 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6916,19 +6916,19 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AQ36" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -7038,25 +7038,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7166,25 +7166,25 @@
         <v>346</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7298,19 +7298,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7418,25 +7418,25 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7549,25 +7549,25 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7680,16 +7680,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7805,25 +7805,25 @@
         <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7936,16 +7936,16 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8059,25 +8059,25 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -8190,16 +8190,16 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8313,25 +8313,25 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8439,25 +8439,25 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8570,16 +8570,16 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8697,13 +8697,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8823,13 +8823,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8951,13 +8951,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9072,16 +9072,16 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9196,16 +9196,16 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9321,19 +9321,19 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9449,19 +9449,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9581,13 +9581,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9702,16 +9702,16 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9828,16 +9828,16 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9954,16 +9954,16 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10080,16 +10080,16 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10207,13 +10207,13 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10333,13 +10333,13 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10461,13 +10461,13 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10583,22 +10583,22 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AP65" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AO65" t="s" s="2">
+      <c r="AQ65" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>84</v>
@@ -10711,25 +10711,25 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AP66" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
+      <c r="AQ66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR66" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -10842,16 +10842,16 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10967,25 +10967,25 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -11098,16 +11098,16 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11228,16 +11228,16 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11355,13 +11355,13 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11481,13 +11481,13 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11609,13 +11609,13 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11731,22 +11731,22 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AP74" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AO74" t="s" s="2">
+      <c r="AQ74" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>84</v>
@@ -11859,25 +11859,25 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11989,13 +11989,13 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12115,13 +12115,13 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12234,28 +12234,28 @@
         <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -12368,16 +12368,16 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12494,16 +12494,16 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AP80" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12620,16 +12620,16 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AP81" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12748,16 +12748,16 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AP82" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -12876,16 +12876,16 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AP83" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13001,25 +13001,25 @@
         <v>84</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP84" t="s" s="2">
+      <c r="AQ84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="85" hidden="true">
@@ -13132,16 +13132,16 @@
         <v>84</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AP85" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13262,16 +13262,16 @@
         <v>84</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AP86" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13389,13 +13389,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13515,13 +13515,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13643,13 +13643,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13765,22 +13765,22 @@
         <v>84</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AP90" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AO90" t="s" s="2">
+      <c r="AQ90" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ90" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>84</v>
@@ -13893,25 +13893,25 @@
         <v>84</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AP91" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP91" t="s" s="2">
+      <c r="AQ91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -14023,13 +14023,13 @@
         <v>84</v>
       </c>
       <c r="AN92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14149,13 +14149,13 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14268,28 +14268,28 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>84</v>
+        <v>625</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>625</v>
+        <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" hidden="true">
@@ -14402,16 +14402,16 @@
         <v>84</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AP95" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14528,16 +14528,16 @@
         <v>84</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AP96" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14654,16 +14654,16 @@
         <v>84</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AP97" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -14782,16 +14782,16 @@
         <v>84</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AP98" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -14910,16 +14910,16 @@
         <v>84</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN99" t="s" s="2">
+      <c r="AP99" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15035,25 +15035,25 @@
         <v>84</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AM100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AN100" t="s" s="2">
+      <c r="AP100" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AO100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP100" t="s" s="2">
+      <c r="AQ100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR100" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR100" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -15166,16 +15166,16 @@
         <v>84</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO101" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AP101" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1300,7 +1300,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$186</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8095" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7527" uniqueCount="873">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2744,69 +2744,6 @@
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size</t>
-  </si>
-  <si>
-    <t>va-cuff-size</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="8358-4"/&gt;
-    &lt;display value="Blood pressure device cuff size"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -3123,7 +3060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR200"/>
+  <dimension ref="A1:AR186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -26707,1788 +26644,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="D187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AP187" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AQ187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR187" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N188" s="2"/>
-      <c r="O188" s="2"/>
-      <c r="P188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP188" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR188" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O189" s="2"/>
-      <c r="P189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP189" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR189" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="P190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP190" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AQ190" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR190" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AP191" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AQ191" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AR191" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AC192" s="2"/>
-      <c r="AD192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AP192" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AQ192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR192" t="s" s="2">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="D193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="AO193" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AP193" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AQ193" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR193" t="s" s="2">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="194" hidden="true">
-      <c r="A194" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
-      <c r="P194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP194" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ194" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR194" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="195" hidden="true">
-      <c r="A195" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O195" s="2"/>
-      <c r="P195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP195" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AQ195" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR195" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="196" hidden="true">
-      <c r="A196" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="P196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y196" s="2"/>
-      <c r="Z196" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AP196" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AQ196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR196" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="197" hidden="true">
-      <c r="A197" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="C197" s="2"/>
-      <c r="D197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E197" s="2"/>
-      <c r="F197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G197" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J197" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K197" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L197" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q197" s="2"/>
-      <c r="R197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF197" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO197" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AP197" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AQ197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR197" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="198" hidden="true">
-      <c r="A198" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C198" s="2"/>
-      <c r="D198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E198" s="2"/>
-      <c r="F198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G198" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H198" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K198" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L198" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="O198" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="P198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q198" s="2"/>
-      <c r="R198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X198" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y198" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="Z198" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AA198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF198" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="AG198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH198" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI198" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AJ198" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO198" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AP198" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AQ198" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR198" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="199" hidden="true">
-      <c r="A199" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C199" s="2"/>
-      <c r="D199" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G199" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K199" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L199" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="P199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q199" s="2"/>
-      <c r="R199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X199" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="Z199" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AA199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF199" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AG199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH199" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ199" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN199" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AO199" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AP199" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AQ199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR199" t="s" s="2">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="200" hidden="true">
-      <c r="A200" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="C200" s="2"/>
-      <c r="D200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E200" s="2"/>
-      <c r="F200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G200" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K200" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L200" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="P200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q200" s="2"/>
-      <c r="R200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="AG200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH200" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ200" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO200" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AP200" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AQ200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR200" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AR200">
+  <autoFilter ref="A1:AR186">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28498,7 +26655,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI199">
+  <conditionalFormatting sqref="A2:AI185">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMeasurementDevice</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsMeasurementDevice</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -605,7 +605,7 @@
     <t>Observation.extension:observation-bodyPosition.value[x]</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodyPosition</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsBodyPosition</t>
   </si>
   <si>
     <t>1804: terminologyMaps using VF_VitalsBodyPosition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -1257,7 +1257,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsCodes</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1793,7 +1793,7 @@
 </t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFVitalsUnits</t>
+    <t>http://va.gov/fhir/ConceptMap/VitalsUnits</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.value</t>
@@ -1915,7 +1915,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodySite</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsBodySite</t>
   </si>
   <si>
     <t>662: terminologyMaps using VF_VitalsBodySite on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -1948,7 +1948,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsMethod</t>
   </si>
   <si>
     <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2671,7 +2671,7 @@
     <t>Observation.component.value[x].coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsPrecondition</t>
   </si>
   <si>
     <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2728,7 +2728,7 @@
     <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsQualifyingDevice</t>
   </si>
   <si>
     <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -3088,7 +3088,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7527" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7527" uniqueCount="880">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -916,6 +916,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-655:if null then fixed value #final {null}VitalSignsSpO2-656:if not null then fixed value #entered-in-error {null}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
@@ -2405,6 +2409,10 @@
     <t>Observation.component.code.coding.system</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-1239-2:if VUID = 4500637 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
     <t>1239-2: fixed value = http://loinc.org case VUID = 4500637</t>
   </si>
   <si>
@@ -2420,6 +2428,10 @@
     <t>Observation.component.code.coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-1239-3:if VUID = 4500637 then fixed value 3151-8 {null}</t>
+  </si>
+  <si>
     <t>1239-3: fixed value = 3151-8 case VUID = 4500637</t>
   </si>
   <si>
@@ -2496,6 +2508,10 @@
   </si>
   <si>
     <t>L/min</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-1239-1:if VUID = 4500637 then fixed value L/min {null}</t>
   </si>
   <si>
     <t>1239-1: fixed value = L/min case VUID = 4500637</t>
@@ -2557,6 +2573,10 @@
     <t>Observation.component:Concentration.code.coding.system</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-1240-2:if VUID = 4500637 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
     <t>1240-2: fixed value = http://loinc.org case VUID = 4500637</t>
   </si>
   <si>
@@ -2566,6 +2586,10 @@
     <t>Observation.component:Concentration.code.coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-1240-3:if VUID = 4500637 then fixed value 3150-0 {null}</t>
+  </si>
+  <si>
     <t>1240-3: fixed value = 3150-0 case VUID = 4500637</t>
   </si>
   <si>
@@ -2606,6 +2630,10 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsSpO2-1240-1:if VUID = 4500637 then fixed value % {null}</t>
   </si>
   <si>
     <t>1240-1: fixed value = % case VUID = 4500637</t>
@@ -2647,7 +2675,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>1802-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+    <t>1802-1: fixed value = http://loinc.org#104158-1 "Associated precondition - Reported"</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition.value[x]</t>
@@ -2710,7 +2738,7 @@
     <t>Observation.component:va-pre-condition-device.code</t>
   </si>
   <si>
-    <t>1803-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+    <t>1803-1: fixed value = http://loinc.org#104158-1 "Associated precondition - Reported"</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.value[x]</t>
@@ -7103,28 +7131,28 @@
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -7132,10 +7160,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7161,16 +7189,16 @@
         <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -7180,7 +7208,7 @@
         <v>84</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>84</v>
@@ -7198,16 +7226,16 @@
         <v>118</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7217,7 +7245,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -7232,7 +7260,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -7247,10 +7275,10 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -7258,13 +7286,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7289,16 +7317,16 @@
         <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -7326,10 +7354,10 @@
         <v>118</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -7347,7 +7375,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7377,10 +7405,10 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -7388,10 +7416,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7512,10 +7540,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7638,10 +7666,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7664,19 +7692,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7725,7 +7753,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7752,10 +7780,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7766,10 +7794,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7890,10 +7918,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8016,10 +8044,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8045,23 +8073,23 @@
         <v>108</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>84</v>
@@ -8103,7 +8131,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -8130,10 +8158,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -8144,10 +8172,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8173,13 +8201,13 @@
         <v>208</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8229,7 +8257,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8256,10 +8284,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -8270,10 +8298,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8299,21 +8327,21 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>84</v>
@@ -8355,7 +8383,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8382,10 +8410,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8396,10 +8424,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8425,14 +8453,14 @@
         <v>208</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8481,7 +8509,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8508,10 +8536,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8522,10 +8550,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8548,19 +8576,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8609,7 +8637,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8636,10 +8664,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8650,10 +8678,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8679,16 +8707,16 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8737,7 +8765,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8764,10 +8792,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8778,14 +8806,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8807,16 +8835,16 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8844,10 +8872,10 @@
         <v>226</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8865,7 +8893,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -8886,30 +8914,30 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9030,10 +9058,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9156,10 +9184,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9167,7 +9195,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>83</v>
@@ -9182,19 +9210,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -9223,13 +9251,13 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -9239,7 +9267,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9282,10 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>84</v>
@@ -9266,10 +9294,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -9280,13 +9308,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>84</v>
@@ -9308,19 +9336,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9330,7 +9358,7 @@
         <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>84</v>
@@ -9369,7 +9397,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9396,10 +9424,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9410,13 +9438,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9438,19 +9466,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9460,7 +9488,7 @@
         <v>84</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>84</v>
@@ -9499,7 +9527,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9526,10 +9554,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9540,10 +9568,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9569,16 +9597,16 @@
         <v>208</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9627,7 +9655,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9654,10 +9682,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9668,10 +9696,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9694,19 +9722,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9755,7 +9783,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9770,25 +9798,25 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -9796,10 +9824,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9822,16 +9850,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9881,7 +9909,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9908,13 +9936,13 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9922,14 +9950,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9948,19 +9976,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -10009,7 +10037,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -10030,19 +10058,19 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>84</v>
@@ -10050,14 +10078,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -10076,19 +10104,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -10125,7 +10153,7 @@
         <v>84</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
@@ -10135,7 +10163,7 @@
         <v>143</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -10144,10 +10172,10 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -10156,19 +10184,19 @@
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -10176,16 +10204,16 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -10204,19 +10232,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -10265,7 +10293,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10274,31 +10302,31 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>84</v>
@@ -10306,10 +10334,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10332,16 +10360,16 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10391,7 +10419,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10406,10 +10434,10 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>84</v>
@@ -10418,13 +10446,13 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -10432,10 +10460,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10458,17 +10486,17 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10517,7 +10545,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10532,25 +10560,25 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>84</v>
@@ -10558,10 +10586,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10584,19 +10612,19 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10624,16 +10652,16 @@
         <v>226</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -10643,7 +10671,7 @@
         <v>143</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10652,7 +10680,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10667,30 +10695,30 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>84</v>
@@ -10712,19 +10740,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10752,10 +10780,10 @@
         <v>226</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -10773,7 +10801,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10782,7 +10810,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -10797,27 +10825,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10938,10 +10966,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11064,10 +11092,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11090,19 +11118,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -11151,7 +11179,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -11166,10 +11194,10 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>84</v>
@@ -11178,10 +11206,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -11192,10 +11220,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11221,20 +11249,20 @@
         <v>114</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>84</v>
@@ -11258,10 +11286,10 @@
         <v>174</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -11279,7 +11307,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11306,10 +11334,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -11320,10 +11348,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11349,14 +11377,14 @@
         <v>208</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11405,7 +11433,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11432,10 +11460,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11446,10 +11474,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11475,14 +11503,14 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11531,7 +11559,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11540,7 +11568,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -11558,10 +11586,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11572,10 +11600,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11601,16 +11629,16 @@
         <v>114</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11659,7 +11687,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11674,10 +11702,10 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>84</v>
@@ -11686,10 +11714,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11700,10 +11728,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11729,10 +11757,10 @@
         <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11824,10 +11852,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11946,13 +11974,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="B71" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="C71" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>84</v>
@@ -11974,16 +12002,16 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12074,10 +12102,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12198,10 +12226,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12322,10 +12350,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12365,7 +12393,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>84</v>
@@ -12448,10 +12476,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12474,7 +12502,7 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>172</v>
@@ -12492,7 +12520,7 @@
         <v>84</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>84</v>
@@ -12572,10 +12600,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12601,10 +12629,10 @@
         <v>208</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12655,7 +12683,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12696,10 +12724,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12725,16 +12753,16 @@
         <v>171</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12762,10 +12790,10 @@
         <v>226</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12783,7 +12811,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12792,13 +12820,13 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>84</v>
@@ -12813,7 +12841,7 @@
         <v>137</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12824,14 +12852,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12853,16 +12881,16 @@
         <v>171</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12890,10 +12918,10 @@
         <v>226</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12911,7 +12939,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12935,27 +12963,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12978,19 +13006,19 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -13039,7 +13067,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13066,10 +13094,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -13080,10 +13108,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13109,13 +13137,13 @@
         <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13145,7 +13173,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -13163,7 +13191,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13178,7 +13206,7 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>84</v>
@@ -13187,27 +13215,27 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13233,16 +13261,16 @@
         <v>171</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -13271,7 +13299,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -13289,7 +13317,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13304,7 +13332,7 @@
         <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>84</v>
@@ -13316,10 +13344,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13330,10 +13358,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13356,16 +13384,16 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13415,7 +13443,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13439,27 +13467,27 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13482,16 +13510,16 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13541,7 +13569,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13565,27 +13593,27 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13608,19 +13636,19 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13669,7 +13697,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13681,7 +13709,7 @@
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13696,10 +13724,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13710,10 +13738,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13834,10 +13862,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13960,14 +13988,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13989,10 +14017,10 @@
         <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>195</v>
@@ -14047,7 +14075,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14088,10 +14116,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14114,13 +14142,13 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14171,7 +14199,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14180,7 +14208,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -14198,10 +14226,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14212,10 +14240,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14238,13 +14266,13 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14295,7 +14323,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14304,7 +14332,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -14322,10 +14350,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14336,10 +14364,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14365,16 +14393,16 @@
         <v>171</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14402,10 +14430,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
@@ -14423,7 +14451,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14447,13 +14475,13 @@
         <v>84</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14464,10 +14492,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14493,16 +14521,16 @@
         <v>171</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14527,13 +14555,13 @@
         <v>84</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -14551,7 +14579,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14575,13 +14603,13 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14592,10 +14620,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14618,17 +14646,17 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14677,7 +14705,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14707,7 +14735,7 @@
         <v>84</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14718,10 +14746,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14747,10 +14775,10 @@
         <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14801,7 +14829,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14828,10 +14856,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14842,10 +14870,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14868,16 +14896,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14927,7 +14955,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14954,10 +14982,10 @@
         <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14968,10 +14996,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14994,16 +15022,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15053,7 +15081,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15080,10 +15108,10 @@
         <v>84</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -15094,10 +15122,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15120,19 +15148,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -15169,7 +15197,7 @@
         <v>84</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -15179,7 +15207,7 @@
         <v>143</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15191,7 +15219,7 @@
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -15206,10 +15234,10 @@
         <v>84</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -15220,10 +15248,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15344,10 +15372,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15470,14 +15498,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15499,10 +15527,10 @@
         <v>139</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>195</v>
@@ -15557,7 +15585,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15598,10 +15626,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15627,16 +15655,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15664,10 +15692,10 @@
         <v>226</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15685,7 +15713,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -15709,16 +15737,16 @@
         <v>84</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>84</v>
@@ -15726,10 +15754,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15752,19 +15780,19 @@
         <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15792,10 +15820,10 @@
         <v>226</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15813,7 +15841,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15822,7 +15850,7 @@
         <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>106</v>
@@ -15837,27 +15865,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15883,16 +15911,16 @@
         <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15920,10 +15948,10 @@
         <v>226</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15941,7 +15969,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15950,13 +15978,13 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>84</v>
@@ -15971,7 +15999,7 @@
         <v>137</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15982,14 +16010,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -16011,16 +16039,16 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16048,10 +16076,10 @@
         <v>226</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
@@ -16069,7 +16097,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16093,27 +16121,27 @@
         <v>84</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16139,16 +16167,16 @@
         <v>85</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -16197,7 +16225,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -16224,10 +16252,10 @@
         <v>84</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -16238,13 +16266,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>84</v>
@@ -16266,19 +16294,19 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16327,7 +16355,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16339,7 +16367,7 @@
         <v>84</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>84</v>
@@ -16354,10 +16382,10 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -16368,10 +16396,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16492,10 +16520,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16618,14 +16646,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -16647,10 +16675,10 @@
         <v>139</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>195</v>
@@ -16705,7 +16733,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16746,10 +16774,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16775,16 +16803,16 @@
         <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16794,7 +16822,7 @@
         <v>84</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>84</v>
@@ -16812,10 +16840,10 @@
         <v>226</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16833,7 +16861,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>94</v>
@@ -16857,16 +16885,16 @@
         <v>84</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>84</v>
@@ -16874,10 +16902,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16998,10 +17026,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17124,10 +17152,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17150,19 +17178,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -17211,7 +17239,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17238,10 +17266,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17252,10 +17280,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17376,10 +17404,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17502,10 +17530,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17531,16 +17559,16 @@
         <v>108</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17589,7 +17617,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17601,10 +17629,10 @@
         <v>84</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>106</v>
+        <v>764</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>84</v>
@@ -17616,10 +17644,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17630,10 +17658,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17659,13 +17687,13 @@
         <v>208</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17715,7 +17743,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17742,10 +17770,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17756,10 +17784,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17785,14 +17813,14 @@
         <v>114</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17841,7 +17869,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17853,10 +17881,10 @@
         <v>84</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>106</v>
+        <v>770</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>84</v>
@@ -17868,10 +17896,10 @@
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17882,10 +17910,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17911,14 +17939,14 @@
         <v>208</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17967,7 +17995,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17994,10 +18022,10 @@
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -18008,10 +18036,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18034,19 +18062,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -18095,7 +18123,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -18122,10 +18150,10 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -18136,10 +18164,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18165,16 +18193,16 @@
         <v>208</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -18223,7 +18251,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -18250,10 +18278,10 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -18264,10 +18292,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18290,19 +18318,19 @@
         <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18330,10 +18358,10 @@
         <v>226</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18351,7 +18379,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18360,7 +18388,7 @@
         <v>94</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>106</v>
@@ -18375,27 +18403,27 @@
         <v>84</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18516,10 +18544,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18642,10 +18670,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18668,19 +18696,19 @@
         <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18729,7 +18757,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18744,10 +18772,10 @@
         <v>106</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>84</v>
@@ -18756,10 +18784,10 @@
         <v>84</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
@@ -18770,10 +18798,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18799,20 +18827,20 @@
         <v>114</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q125" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R125" t="s" s="2">
         <v>84</v>
@@ -18836,10 +18864,10 @@
         <v>174</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18857,7 +18885,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18884,10 +18912,10 @@
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
@@ -18898,10 +18926,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18927,14 +18955,14 @@
         <v>208</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18983,7 +19011,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19010,10 +19038,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
@@ -19024,10 +19052,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19053,21 +19081,21 @@
         <v>108</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>84</v>
@@ -19109,7 +19137,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19118,7 +19146,7 @@
         <v>94</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>106</v>
@@ -19136,10 +19164,10 @@
         <v>84</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -19150,10 +19178,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19179,23 +19207,23 @@
         <v>114</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>84</v>
@@ -19237,7 +19265,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19249,10 +19277,10 @@
         <v>84</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>106</v>
+        <v>797</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>84</v>
@@ -19264,10 +19292,10 @@
         <v>84</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -19278,10 +19306,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19307,16 +19335,16 @@
         <v>171</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19344,10 +19372,10 @@
         <v>226</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>84</v>
@@ -19365,7 +19393,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19374,7 +19402,7 @@
         <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -19395,7 +19423,7 @@
         <v>137</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19406,14 +19434,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -19435,16 +19463,16 @@
         <v>171</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19472,10 +19500,10 @@
         <v>226</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19493,7 +19521,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19517,27 +19545,27 @@
         <v>84</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19563,16 +19591,16 @@
         <v>85</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19621,7 +19649,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19648,10 +19676,10 @@
         <v>84</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
@@ -19662,13 +19690,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>84</v>
@@ -19690,19 +19718,19 @@
         <v>95</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19751,7 +19779,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19763,7 +19791,7 @@
         <v>84</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>84</v>
@@ -19778,10 +19806,10 @@
         <v>84</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
@@ -19792,10 +19820,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19916,10 +19944,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20042,14 +20070,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -20071,10 +20099,10 @@
         <v>139</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>195</v>
@@ -20129,7 +20157,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20170,10 +20198,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20199,16 +20227,16 @@
         <v>171</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -20218,7 +20246,7 @@
         <v>84</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>84</v>
@@ -20236,10 +20264,10 @@
         <v>226</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>84</v>
@@ -20257,7 +20285,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>94</v>
@@ -20281,16 +20309,16 @@
         <v>84</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>84</v>
@@ -20298,10 +20326,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20422,10 +20450,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20548,10 +20576,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20574,19 +20602,19 @@
         <v>95</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>84</v>
@@ -20635,7 +20663,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20662,10 +20690,10 @@
         <v>84</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
@@ -20676,10 +20704,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20800,10 +20828,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20926,10 +20954,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20955,16 +20983,16 @@
         <v>108</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>84</v>
@@ -21013,7 +21041,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21025,10 +21053,10 @@
         <v>84</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>106</v>
+        <v>816</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>84</v>
@@ -21040,10 +21068,10 @@
         <v>84</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ142" t="s" s="2">
         <v>84</v>
@@ -21054,10 +21082,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21083,13 +21111,13 @@
         <v>208</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -21139,7 +21167,7 @@
         <v>84</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
@@ -21166,10 +21194,10 @@
         <v>84</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>84</v>
@@ -21180,10 +21208,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21209,14 +21237,14 @@
         <v>114</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>84</v>
@@ -21265,7 +21293,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21277,10 +21305,10 @@
         <v>84</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>106</v>
+        <v>820</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>84</v>
@@ -21292,10 +21320,10 @@
         <v>84</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
@@ -21306,10 +21334,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21335,14 +21363,14 @@
         <v>208</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>84</v>
@@ -21391,7 +21419,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21418,10 +21446,10 @@
         <v>84</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
@@ -21432,10 +21460,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21458,19 +21486,19 @@
         <v>95</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21519,7 +21547,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21546,10 +21574,10 @@
         <v>84</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21560,10 +21588,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21589,16 +21617,16 @@
         <v>208</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>84</v>
@@ -21647,7 +21675,7 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>82</v>
@@ -21674,10 +21702,10 @@
         <v>84</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
@@ -21688,10 +21716,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21714,19 +21742,19 @@
         <v>95</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>84</v>
@@ -21754,10 +21782,10 @@
         <v>226</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>84</v>
@@ -21775,7 +21803,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>82</v>
@@ -21784,7 +21812,7 @@
         <v>94</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>106</v>
@@ -21799,27 +21827,27 @@
         <v>84</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ148" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21940,10 +21968,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22066,10 +22094,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22092,19 +22120,19 @@
         <v>95</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>84</v>
@@ -22153,7 +22181,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22168,10 +22196,10 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>84</v>
@@ -22180,10 +22208,10 @@
         <v>84</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
@@ -22194,10 +22222,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22223,20 +22251,20 @@
         <v>114</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q152" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R152" t="s" s="2">
         <v>84</v>
@@ -22260,10 +22288,10 @@
         <v>174</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>84</v>
@@ -22281,7 +22309,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22308,10 +22336,10 @@
         <v>84</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
@@ -22322,10 +22350,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22351,14 +22379,14 @@
         <v>208</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>84</v>
@@ -22407,7 +22435,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22434,10 +22462,10 @@
         <v>84</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
@@ -22448,10 +22476,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22477,21 +22505,21 @@
         <v>108</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>84</v>
@@ -22533,7 +22561,7 @@
         <v>84</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>82</v>
@@ -22542,7 +22570,7 @@
         <v>94</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>106</v>
@@ -22560,10 +22588,10 @@
         <v>84</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>84</v>
@@ -22574,10 +22602,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22603,23 +22631,23 @@
         <v>114</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>84</v>
@@ -22661,7 +22689,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22673,10 +22701,10 @@
         <v>84</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>106</v>
+        <v>835</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>84</v>
@@ -22688,10 +22716,10 @@
         <v>84</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
@@ -22702,10 +22730,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22731,16 +22759,16 @@
         <v>171</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>84</v>
@@ -22768,10 +22796,10 @@
         <v>226</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>84</v>
@@ -22789,7 +22817,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22798,7 +22826,7 @@
         <v>94</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>106</v>
@@ -22819,7 +22847,7 @@
         <v>137</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>84</v>
@@ -22830,14 +22858,14 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -22859,16 +22887,16 @@
         <v>171</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>84</v>
@@ -22896,10 +22924,10 @@
         <v>226</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>84</v>
@@ -22917,7 +22945,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -22941,27 +22969,27 @@
         <v>84</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22987,16 +23015,16 @@
         <v>85</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23045,7 +23073,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23072,10 +23100,10 @@
         <v>84</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
@@ -23086,13 +23114,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>84</v>
@@ -23114,19 +23142,19 @@
         <v>95</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
@@ -23175,7 +23203,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23187,7 +23215,7 @@
         <v>84</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>84</v>
@@ -23202,10 +23230,10 @@
         <v>84</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
@@ -23216,10 +23244,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23340,10 +23368,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23466,14 +23494,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -23495,10 +23523,10 @@
         <v>139</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>195</v>
@@ -23553,7 +23581,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23594,10 +23622,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23623,16 +23651,16 @@
         <v>171</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>84</v>
@@ -23642,7 +23670,7 @@
         <v>84</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>84</v>
@@ -23660,10 +23688,10 @@
         <v>226</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>84</v>
@@ -23681,7 +23709,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>94</v>
@@ -23696,7 +23724,7 @@
         <v>106</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>84</v>
@@ -23705,16 +23733,16 @@
         <v>84</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>84</v>
@@ -23722,10 +23750,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23748,19 +23776,19 @@
         <v>95</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>84</v>
@@ -23788,16 +23816,16 @@
         <v>226</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AC164" s="2"/>
       <c r="AD164" t="s" s="2">
@@ -23807,7 +23835,7 @@
         <v>143</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -23816,7 +23844,7 @@
         <v>94</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>106</v>
@@ -23831,30 +23859,30 @@
         <v>84</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR164" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>84</v>
@@ -23879,16 +23907,16 @@
         <v>171</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>84</v>
@@ -23916,10 +23944,10 @@
         <v>226</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>84</v>
@@ -23937,7 +23965,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -23946,7 +23974,7 @@
         <v>94</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>106</v>
@@ -23961,27 +23989,27 @@
         <v>84</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR165" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24102,10 +24130,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24228,10 +24256,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24254,19 +24282,19 @@
         <v>95</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>84</v>
@@ -24295,7 +24323,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>84</v>
@@ -24313,7 +24341,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24328,7 +24356,7 @@
         <v>106</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>84</v>
@@ -24340,10 +24368,10 @@
         <v>84</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24354,10 +24382,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24383,16 +24411,16 @@
         <v>208</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>84</v>
@@ -24441,7 +24469,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24468,10 +24496,10 @@
         <v>84</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24482,10 +24510,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24511,16 +24539,16 @@
         <v>171</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>84</v>
@@ -24548,10 +24576,10 @@
         <v>226</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>84</v>
@@ -24569,7 +24597,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24578,7 +24606,7 @@
         <v>94</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>106</v>
@@ -24599,7 +24627,7 @@
         <v>137</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>
@@ -24610,14 +24638,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -24639,16 +24667,16 @@
         <v>171</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>84</v>
@@ -24676,10 +24704,10 @@
         <v>226</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>84</v>
@@ -24697,7 +24725,7 @@
         <v>84</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>82</v>
@@ -24721,27 +24749,27 @@
         <v>84</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ171" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR171" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24767,16 +24795,16 @@
         <v>85</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>84</v>
@@ -24825,7 +24853,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -24852,10 +24880,10 @@
         <v>84</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ172" t="s" s="2">
         <v>84</v>
@@ -24866,13 +24894,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>84</v>
@@ -24894,19 +24922,19 @@
         <v>95</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>84</v>
@@ -24955,7 +24983,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>82</v>
@@ -24967,7 +24995,7 @@
         <v>84</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>84</v>
@@ -24982,10 +25010,10 @@
         <v>84</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AQ173" t="s" s="2">
         <v>84</v>
@@ -24996,10 +25024,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25120,10 +25148,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25246,14 +25274,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -25275,10 +25303,10 @@
         <v>139</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>195</v>
@@ -25333,7 +25361,7 @@
         <v>84</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>82</v>
@@ -25374,10 +25402,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25403,16 +25431,16 @@
         <v>171</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>84</v>
@@ -25422,7 +25450,7 @@
         <v>84</v>
       </c>
       <c r="S177" t="s" s="2">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="T177" t="s" s="2">
         <v>84</v>
@@ -25440,10 +25468,10 @@
         <v>226</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>84</v>
@@ -25461,7 +25489,7 @@
         <v>84</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>94</v>
@@ -25476,7 +25504,7 @@
         <v>106</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>84</v>
@@ -25485,16 +25513,16 @@
         <v>84</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP177" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ177" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR177" t="s" s="2">
         <v>84</v>
@@ -25502,10 +25530,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25528,19 +25556,19 @@
         <v>95</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>84</v>
@@ -25568,16 +25596,16 @@
         <v>226</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
@@ -25587,7 +25615,7 @@
         <v>143</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>82</v>
@@ -25596,7 +25624,7 @@
         <v>94</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>106</v>
@@ -25611,30 +25639,30 @@
         <v>84</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP178" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ178" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR178" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>84</v>
@@ -25659,16 +25687,16 @@
         <v>171</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>84</v>
@@ -25696,10 +25724,10 @@
         <v>226</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>84</v>
@@ -25717,7 +25745,7 @@
         <v>84</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>82</v>
@@ -25726,7 +25754,7 @@
         <v>94</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>106</v>
@@ -25741,27 +25769,27 @@
         <v>84</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ179" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR179" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25882,10 +25910,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26008,10 +26036,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26034,19 +26062,19 @@
         <v>95</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>84</v>
@@ -26075,7 +26103,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>84</v>
@@ -26093,7 +26121,7 @@
         <v>84</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>82</v>
@@ -26108,7 +26136,7 @@
         <v>106</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>84</v>
@@ -26120,10 +26148,10 @@
         <v>84</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ182" t="s" s="2">
         <v>84</v>
@@ -26134,10 +26162,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26163,16 +26191,16 @@
         <v>208</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>84</v>
@@ -26221,7 +26249,7 @@
         <v>84</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>82</v>
@@ -26248,10 +26276,10 @@
         <v>84</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ183" t="s" s="2">
         <v>84</v>
@@ -26262,10 +26290,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26291,16 +26319,16 @@
         <v>171</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>84</v>
@@ -26328,10 +26356,10 @@
         <v>226</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>84</v>
@@ -26349,7 +26377,7 @@
         <v>84</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>82</v>
@@ -26358,7 +26386,7 @@
         <v>94</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>106</v>
@@ -26379,7 +26407,7 @@
         <v>137</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AQ184" t="s" s="2">
         <v>84</v>
@@ -26390,14 +26418,14 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
@@ -26419,16 +26447,16 @@
         <v>171</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>84</v>
@@ -26456,10 +26484,10 @@
         <v>226</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>84</v>
@@ -26477,7 +26505,7 @@
         <v>84</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>82</v>
@@ -26501,27 +26529,27 @@
         <v>84</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ185" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR185" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26547,16 +26575,16 @@
         <v>85</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>84</v>
@@ -26605,7 +26633,7 @@
         <v>84</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>82</v>
@@ -26632,10 +26660,10 @@
         <v>84</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP186" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ186" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,7 +919,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-655:if null then fixed value #final {null}VitalSignsSpO2-656:if not null then fixed value #entered-in-error {null}</t>
+vsso-14-655:120.5-4: if null then #final {null}vsso-14-656:120.5-4: if not null then #entered-in-error {null}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
@@ -2410,7 +2410,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-1239-2:if VUID = 4500637 then fixed value http://loinc.org {null}</t>
+vsso-14-1239-2:undefined: if VUID = 4500637 then http://loinc.org {null}</t>
   </si>
   <si>
     <t>1239-2: fixed value = http://loinc.org case VUID = 4500637</t>
@@ -2429,7 +2429,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-1239-3:if VUID = 4500637 then fixed value 3151-8 {null}</t>
+vsso-14-1239-3:undefined: if VUID = 4500637 then 3151-8 {null}</t>
   </si>
   <si>
     <t>1239-3: fixed value = 3151-8 case VUID = 4500637</t>
@@ -2511,7 +2511,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-1239-1:if VUID = 4500637 then fixed value L/min {null}</t>
+vsso-14-1239-1:undefined: if VUID = 4500637 then L/min {null}</t>
   </si>
   <si>
     <t>1239-1: fixed value = L/min case VUID = 4500637</t>
@@ -2574,7 +2574,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-1240-2:if VUID = 4500637 then fixed value http://loinc.org {null}</t>
+vsso-14-1240-2:undefined: if VUID = 4500637 then http://loinc.org {null}</t>
   </si>
   <si>
     <t>1240-2: fixed value = http://loinc.org case VUID = 4500637</t>
@@ -2587,7 +2587,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-1240-3:if VUID = 4500637 then fixed value 3150-0 {null}</t>
+vsso-14-1240-3:undefined: if VUID = 4500637 then 3150-0 {null}</t>
   </si>
   <si>
     <t>1240-3: fixed value = 3150-0 case VUID = 4500637</t>
@@ -2633,7 +2633,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsSpO2-1240-1:if VUID = 4500637 then fixed value % {null}</t>
+vsso-14-1240-1:undefined: if VUID = 4500637 then % {null}</t>
   </si>
   <si>
     <t>1240-1: fixed value = % case VUID = 4500637</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="888">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -577,6 +577,9 @@
     <t>663: terminologyMaps using VF_VitalsMeasurementDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
+    <t>Observation.ObservationMethods</t>
+  </si>
+  <si>
     <t>Observation.extension:observation-bodyPosition</t>
   </si>
   <si>
@@ -928,7 +931,7 @@
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
-    <t>vital.removed [m]</t>
+    <t>Observation.ObservationExtension.Removed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1280,7 +1283,7 @@
     <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
-    <t>vital.vuid,vital.name,vital.high,vital.low,vital.bmi</t>
+    <t>Observation.ObservationCode,Observation.ObservationExtension.BMI</t>
   </si>
   <si>
     <t>Observation.code.coding:PulseOx</t>
@@ -1464,7 +1467,7 @@
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>vital.taken</t>
+    <t>Observation.Observation.Description,Observation.ObservationMethod.Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1489,9 +1492,6 @@
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
   </si>
   <si>
-    <t>vital.entered</t>
-  </si>
-  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1523,7 +1523,7 @@
     <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
-    <t>vital.facility,vital.location</t>
+    <t>Observation.EnteredAt,Observation.ObservationExtension.Location</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1632,7 +1632,7 @@
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
-    <t>vital.value,vital.units,vital.metricvalue,vital.metricUnits,vital.bmi</t>
+    <t>Observation.ObservationValue,Observation.ObservationExtension.BMI</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -2499,6 +2499,9 @@
   </si>
   <si>
     <t>Vital.VitalSign.SupplementalO2</t>
+  </si>
+  <si>
+    <t>Observation.ObservationExtension.SupplementalO2</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.value[x].comparator</t>
@@ -3149,7 +3152,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="60.49609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="76.37109375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -4937,7 +4940,7 @@
         <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>85</v>
@@ -4960,13 +4963,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>139</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>85</v>
@@ -4988,13 +4991,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -5089,7 +5092,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>153</v>
@@ -5216,7 +5219,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>160</v>
@@ -5343,7 +5346,7 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>164</v>
@@ -5386,7 +5389,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>85</v>
@@ -5472,7 +5475,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>171</v>
@@ -5535,7 +5538,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>85</v>
@@ -5568,13 +5571,13 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>85</v>
@@ -5597,14 +5600,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -5626,16 +5629,16 @@
         <v>140</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>85</v>
@@ -5684,7 +5687,7 @@
         <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -5728,10 +5731,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5754,17 +5757,17 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>85</v>
@@ -5813,7 +5816,7 @@
         <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -5837,19 +5840,19 @@
         <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>85</v>
@@ -5857,10 +5860,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5883,7 +5886,7 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>154</v>
@@ -5984,14 +5987,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -6013,13 +6016,13 @@
         <v>140</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -6113,10 +6116,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -6142,16 +6145,16 @@
         <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -6179,10 +6182,10 @@
         <v>175</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -6200,7 +6203,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -6233,7 +6236,7 @@
         <v>138</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>85</v>
@@ -6244,10 +6247,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6273,16 +6276,16 @@
         <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -6307,13 +6310,13 @@
         <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -6331,7 +6334,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -6361,10 +6364,10 @@
         <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>85</v>
@@ -6375,10 +6378,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6404,16 +6407,16 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>85</v>
@@ -6423,10 +6426,10 @@
         <v>85</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>85</v>
@@ -6462,7 +6465,7 @@
         <v>85</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -6477,7 +6480,7 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>85</v>
@@ -6492,10 +6495,10 @@
         <v>85</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>85</v>
@@ -6506,10 +6509,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6532,16 +6535,16 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6555,7 +6558,7 @@
         <v>85</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>85</v>
@@ -6591,7 +6594,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -6606,7 +6609,7 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>85</v>
@@ -6621,10 +6624,10 @@
         <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>85</v>
@@ -6635,10 +6638,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6661,13 +6664,13 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6718,7 +6721,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6748,10 +6751,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6762,10 +6765,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6788,16 +6791,16 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6847,7 +6850,7 @@
         <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -6877,10 +6880,10 @@
         <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>85</v>
@@ -6891,14 +6894,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6917,17 +6920,17 @@
         <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
@@ -6976,7 +6979,7 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -7000,16 +7003,16 @@
         <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>85</v>
@@ -7020,14 +7023,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -7046,16 +7049,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -7105,7 +7108,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -7129,16 +7132,16 @@
         <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -7149,10 +7152,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -7178,16 +7181,16 @@
         <v>115</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -7216,7 +7219,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>85</v>
@@ -7234,7 +7237,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>95</v>
@@ -7246,31 +7249,31 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>85</v>
@@ -7278,10 +7281,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7307,16 +7310,16 @@
         <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -7326,7 +7329,7 @@
         <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>85</v>
@@ -7344,16 +7347,16 @@
         <v>119</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7363,7 +7366,7 @@
         <v>144</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -7378,7 +7381,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -7396,10 +7399,10 @@
         <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS33" t="s" s="2">
         <v>85</v>
@@ -7407,13 +7410,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -7438,16 +7441,16 @@
         <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -7475,10 +7478,10 @@
         <v>119</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -7496,7 +7499,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -7529,10 +7532,10 @@
         <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS34" t="s" s="2">
         <v>85</v>
@@ -7540,10 +7543,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7566,7 +7569,7 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>154</v>
@@ -7667,14 +7670,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7696,13 +7699,13 @@
         <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7796,10 +7799,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7822,19 +7825,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7883,7 +7886,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7913,10 +7916,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -7927,10 +7930,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7953,7 +7956,7 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>154</v>
@@ -8054,14 +8057,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -8083,13 +8086,13 @@
         <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -8183,10 +8186,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8212,23 +8215,23 @@
         <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>85</v>
@@ -8270,7 +8273,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -8300,10 +8303,10 @@
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
@@ -8314,10 +8317,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8340,16 +8343,16 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8399,7 +8402,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -8429,10 +8432,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -8443,10 +8446,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8472,21 +8475,21 @@
         <v>115</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>85</v>
@@ -8528,7 +8531,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -8558,10 +8561,10 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
@@ -8572,10 +8575,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8598,17 +8601,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -8657,7 +8660,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8687,10 +8690,10 @@
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
@@ -8701,10 +8704,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8727,19 +8730,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8788,7 +8791,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8818,10 +8821,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -8832,10 +8835,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8858,19 +8861,19 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8919,7 +8922,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8949,10 +8952,10 @@
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8963,14 +8966,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8992,16 +8995,16 @@
         <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -9026,13 +9029,13 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -9050,7 +9053,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -9074,30 +9077,30 @@
         <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9120,7 +9123,7 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>154</v>
@@ -9221,14 +9224,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -9250,13 +9253,13 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9350,10 +9353,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9361,7 +9364,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>84</v>
@@ -9376,19 +9379,19 @@
         <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -9417,13 +9420,13 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -9433,7 +9436,7 @@
         <v>144</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9448,13 +9451,13 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>85</v>
@@ -9463,10 +9466,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -9477,13 +9480,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>85</v>
@@ -9505,19 +9508,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -9527,7 +9530,7 @@
         <v>85</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>85</v>
@@ -9566,7 +9569,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9596,10 +9599,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -9610,13 +9613,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>85</v>
@@ -9638,19 +9641,19 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9660,7 +9663,7 @@
         <v>85</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>85</v>
@@ -9699,7 +9702,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9729,10 +9732,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -9743,10 +9746,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9769,19 +9772,19 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9830,7 +9833,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9860,10 +9863,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9874,10 +9877,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9900,19 +9903,19 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9961,7 +9964,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9976,28 +9979,28 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>85</v>
@@ -10005,10 +10008,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -10031,16 +10034,16 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -10090,7 +10093,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -10120,13 +10123,13 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>85</v>
@@ -10134,14 +10137,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -10160,19 +10163,19 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -10221,7 +10224,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -10245,19 +10248,19 @@
         <v>85</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>85</v>
@@ -10265,14 +10268,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -10291,19 +10294,19 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -10340,7 +10343,7 @@
         <v>85</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
@@ -10350,7 +10353,7 @@
         <v>144</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -10359,10 +10362,10 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -10374,19 +10377,19 @@
         <v>85</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AS56" t="s" s="2">
         <v>85</v>
@@ -10394,16 +10397,16 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -10422,19 +10425,19 @@
         <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -10483,7 +10486,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -10492,34 +10495,34 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AS57" t="s" s="2">
         <v>85</v>
@@ -10527,10 +10530,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10553,16 +10556,16 @@
         <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10612,7 +10615,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10627,13 +10630,13 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>471</v>
+        <v>85</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>85</v>
@@ -10848,7 +10851,7 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y60" t="s" s="2">
         <v>493</v>
@@ -10860,7 +10863,7 @@
         <v>85</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -10979,7 +10982,7 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y61" t="s" s="2">
         <v>493</v>
@@ -11073,7 +11076,7 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>154</v>
@@ -11181,7 +11184,7 @@
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -11203,13 +11206,13 @@
         <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -11591,7 +11594,7 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>533</v>
@@ -11928,10 +11931,10 @@
         <v>554</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>85</v>
@@ -11980,7 +11983,7 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>558</v>
@@ -12873,7 +12876,7 @@
         <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>581</v>
@@ -13037,7 +13040,7 @@
         <v>85</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y77" t="s" s="2">
         <v>588</v>
@@ -13168,7 +13171,7 @@
         <v>85</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y78" t="s" s="2">
         <v>599</v>
@@ -13471,7 +13474,7 @@
         <v>85</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>85</v>
@@ -13600,7 +13603,7 @@
         <v>85</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>85</v>
@@ -14038,7 +14041,7 @@
         <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>154</v>
@@ -14146,7 +14149,7 @@
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -14168,13 +14171,13 @@
         <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -14303,10 +14306,10 @@
         <v>664</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>85</v>
@@ -15070,7 +15073,7 @@
         <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>701</v>
@@ -15584,7 +15587,7 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>154</v>
@@ -15692,7 +15695,7 @@
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -15714,13 +15717,13 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15849,10 +15852,10 @@
         <v>664</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>85</v>
@@ -16008,13 +16011,13 @@
         <v>85</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>85</v>
@@ -16062,13 +16065,13 @@
         <v>733</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>85</v>
@@ -16139,7 +16142,7 @@
         <v>85</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
         <v>493</v>
@@ -16270,7 +16273,7 @@
         <v>85</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y102" t="s" s="2">
         <v>588</v>
@@ -16401,7 +16404,7 @@
         <v>85</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y103" t="s" s="2">
         <v>599</v>
@@ -16759,7 +16762,7 @@
         <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>154</v>
@@ -16867,7 +16870,7 @@
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -16889,13 +16892,13 @@
         <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -17024,10 +17027,10 @@
         <v>664</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
@@ -17183,13 +17186,13 @@
         <v>85</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>85</v>
@@ -17237,13 +17240,13 @@
         <v>733</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS109" t="s" s="2">
         <v>85</v>
@@ -17277,7 +17280,7 @@
         <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>154</v>
@@ -17385,7 +17388,7 @@
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -17407,13 +17410,13 @@
         <v>140</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -17533,19 +17536,19 @@
         <v>96</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>85</v>
@@ -17594,7 +17597,7 @@
         <v>85</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -17624,10 +17627,10 @@
         <v>85</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
@@ -17664,7 +17667,7 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>154</v>
@@ -17772,7 +17775,7 @@
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -17794,13 +17797,13 @@
         <v>140</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -17923,16 +17926,16 @@
         <v>109</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>85</v>
@@ -17981,7 +17984,7 @@
         <v>85</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
@@ -18011,10 +18014,10 @@
         <v>85</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>85</v>
@@ -18051,16 +18054,16 @@
         <v>96</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -18110,7 +18113,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -18140,10 +18143,10 @@
         <v>85</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
@@ -18183,14 +18186,14 @@
         <v>115</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -18239,7 +18242,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -18269,10 +18272,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -18309,17 +18312,17 @@
         <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
@@ -18368,7 +18371,7 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -18398,10 +18401,10 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
@@ -18438,19 +18441,19 @@
         <v>96</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>85</v>
@@ -18499,7 +18502,7 @@
         <v>85</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -18529,10 +18532,10 @@
         <v>85</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>85</v>
@@ -18569,19 +18572,19 @@
         <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>85</v>
@@ -18630,7 +18633,7 @@
         <v>85</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
@@ -18660,10 +18663,10 @@
         <v>85</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>85</v>
@@ -18737,7 +18740,7 @@
         <v>85</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y121" t="s" s="2">
         <v>493</v>
@@ -18831,7 +18834,7 @@
         <v>85</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>154</v>
@@ -18939,7 +18942,7 @@
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -18961,13 +18964,13 @@
         <v>140</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -19169,7 +19172,7 @@
         <v>793</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>85</v>
+        <v>794</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>85</v>
@@ -19192,10 +19195,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19323,10 +19326,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19349,7 +19352,7 @@
         <v>96</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L126" t="s" s="2">
         <v>533</v>
@@ -19452,10 +19455,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19495,7 +19498,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>85</v>
@@ -19581,10 +19584,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19626,7 +19629,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>85</v>
@@ -19680,10 +19683,10 @@
         <v>85</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>85</v>
@@ -19712,7 +19715,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>740</v>
@@ -19775,7 +19778,7 @@
         <v>85</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y129" t="s" s="2">
         <v>588</v>
@@ -19843,7 +19846,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>746</v>
@@ -19906,7 +19909,7 @@
         <v>85</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y130" t="s" s="2">
         <v>599</v>
@@ -19974,7 +19977,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>747</v>
@@ -20105,13 +20108,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>717</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>85</v>
@@ -20136,7 +20139,7 @@
         <v>651</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M132" t="s" s="2">
         <v>753</v>
@@ -20238,7 +20241,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>725</v>
@@ -20264,7 +20267,7 @@
         <v>85</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>154</v>
@@ -20365,14 +20368,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>726</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -20394,13 +20397,13 @@
         <v>140</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -20494,7 +20497,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>727</v>
@@ -20529,10 +20532,10 @@
         <v>664</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>85</v>
@@ -20625,7 +20628,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>728</v>
@@ -20673,7 +20676,7 @@
         <v>85</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>85</v>
@@ -20688,13 +20691,13 @@
         <v>85</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>85</v>
@@ -20742,13 +20745,13 @@
         <v>733</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR136" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS136" t="s" s="2">
         <v>85</v>
@@ -20756,7 +20759,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>760</v>
@@ -20782,7 +20785,7 @@
         <v>85</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>154</v>
@@ -20883,14 +20886,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>762</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20912,13 +20915,13 @@
         <v>140</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -21012,7 +21015,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>764</v>
@@ -21038,19 +21041,19 @@
         <v>96</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>85</v>
@@ -21099,7 +21102,7 @@
         <v>85</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>83</v>
@@ -21129,10 +21132,10 @@
         <v>85</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>85</v>
@@ -21143,7 +21146,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>766</v>
@@ -21169,7 +21172,7 @@
         <v>85</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L140" t="s" s="2">
         <v>154</v>
@@ -21270,14 +21273,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>768</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -21299,13 +21302,13 @@
         <v>140</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -21399,7 +21402,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>770</v>
@@ -21428,16 +21431,16 @@
         <v>109</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>85</v>
@@ -21486,7 +21489,7 @@
         <v>85</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>83</v>
@@ -21498,10 +21501,10 @@
         <v>85</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>85</v>
@@ -21516,10 +21519,10 @@
         <v>85</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>85</v>
@@ -21530,7 +21533,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>774</v>
@@ -21556,16 +21559,16 @@
         <v>96</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -21615,7 +21618,7 @@
         <v>85</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>83</v>
@@ -21645,10 +21648,10 @@
         <v>85</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>85</v>
@@ -21659,7 +21662,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>776</v>
@@ -21688,14 +21691,14 @@
         <v>115</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>85</v>
@@ -21744,7 +21747,7 @@
         <v>85</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>83</v>
@@ -21756,10 +21759,10 @@
         <v>85</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>85</v>
@@ -21774,10 +21777,10 @@
         <v>85</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>85</v>
@@ -21788,7 +21791,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>780</v>
@@ -21814,17 +21817,17 @@
         <v>96</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>85</v>
@@ -21873,7 +21876,7 @@
         <v>85</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>83</v>
@@ -21903,10 +21906,10 @@
         <v>85</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>85</v>
@@ -21917,7 +21920,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>782</v>
@@ -21943,19 +21946,19 @@
         <v>96</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>85</v>
@@ -22004,7 +22007,7 @@
         <v>85</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>83</v>
@@ -22034,10 +22037,10 @@
         <v>85</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>85</v>
@@ -22048,7 +22051,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>784</v>
@@ -22074,19 +22077,19 @@
         <v>96</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>85</v>
@@ -22135,7 +22138,7 @@
         <v>85</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>83</v>
@@ -22165,10 +22168,10 @@
         <v>85</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>85</v>
@@ -22179,7 +22182,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>734</v>
@@ -22242,7 +22245,7 @@
         <v>85</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y148" t="s" s="2">
         <v>493</v>
@@ -22310,7 +22313,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>787</v>
@@ -22336,7 +22339,7 @@
         <v>85</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>154</v>
@@ -22437,14 +22440,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -22466,13 +22469,13 @@
         <v>140</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -22566,7 +22569,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>791</v>
@@ -22668,13 +22671,13 @@
         <v>107</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>793</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>85</v>
+        <v>794</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>85</v>
@@ -22697,10 +22700,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22828,10 +22831,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22854,7 +22857,7 @@
         <v>96</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L153" t="s" s="2">
         <v>533</v>
@@ -22957,10 +22960,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -23000,7 +23003,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>85</v>
@@ -23086,10 +23089,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23131,7 +23134,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>85</v>
@@ -23185,10 +23188,10 @@
         <v>85</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>85</v>
@@ -23217,7 +23220,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>740</v>
@@ -23280,7 +23283,7 @@
         <v>85</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y156" t="s" s="2">
         <v>588</v>
@@ -23348,7 +23351,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>746</v>
@@ -23411,7 +23414,7 @@
         <v>85</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y157" t="s" s="2">
         <v>599</v>
@@ -23479,7 +23482,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>747</v>
@@ -23610,13 +23613,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>717</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>85</v>
@@ -23743,7 +23746,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>725</v>
@@ -23769,7 +23772,7 @@
         <v>85</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>154</v>
@@ -23870,14 +23873,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>726</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -23899,13 +23902,13 @@
         <v>140</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -23999,7 +24002,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>727</v>
@@ -24034,10 +24037,10 @@
         <v>664</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>85</v>
@@ -24130,7 +24133,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>728</v>
@@ -24178,7 +24181,7 @@
         <v>85</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>85</v>
@@ -24193,13 +24196,13 @@
         <v>85</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>85</v>
@@ -24232,7 +24235,7 @@
         <v>107</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>85</v>
@@ -24247,13 +24250,13 @@
         <v>733</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR163" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS163" t="s" s="2">
         <v>85</v>
@@ -24261,7 +24264,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>734</v>
@@ -24324,7 +24327,7 @@
         <v>85</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y164" t="s" s="2">
         <v>493</v>
@@ -24336,7 +24339,7 @@
         <v>85</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AC164" s="2"/>
       <c r="AD164" t="s" s="2">
@@ -24390,13 +24393,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>734</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>85</v>
@@ -24455,7 +24458,7 @@
         <v>85</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y165" t="s" s="2">
         <v>493</v>
@@ -24523,7 +24526,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>787</v>
@@ -24549,7 +24552,7 @@
         <v>85</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>154</v>
@@ -24650,14 +24653,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -24679,13 +24682,13 @@
         <v>140</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -24779,10 +24782,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24805,19 +24808,19 @@
         <v>96</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>85</v>
@@ -24846,7 +24849,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>85</v>
@@ -24864,7 +24867,7 @@
         <v>85</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>83</v>
@@ -24879,13 +24882,13 @@
         <v>107</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>85</v>
@@ -24894,10 +24897,10 @@
         <v>85</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>85</v>
@@ -24908,10 +24911,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24934,19 +24937,19 @@
         <v>96</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>85</v>
@@ -24995,7 +24998,7 @@
         <v>85</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>83</v>
@@ -25025,10 +25028,10 @@
         <v>85</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ169" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR169" t="s" s="2">
         <v>85</v>
@@ -25039,7 +25042,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>740</v>
@@ -25102,7 +25105,7 @@
         <v>85</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y170" t="s" s="2">
         <v>588</v>
@@ -25170,7 +25173,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>746</v>
@@ -25233,7 +25236,7 @@
         <v>85</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y171" t="s" s="2">
         <v>599</v>
@@ -25301,7 +25304,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>747</v>
@@ -25432,13 +25435,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>717</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>85</v>
@@ -25565,7 +25568,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>725</v>
@@ -25591,7 +25594,7 @@
         <v>85</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L174" t="s" s="2">
         <v>154</v>
@@ -25692,14 +25695,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>726</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -25721,13 +25724,13 @@
         <v>140</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -25821,7 +25824,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>727</v>
@@ -25856,10 +25859,10 @@
         <v>664</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>85</v>
@@ -25952,7 +25955,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>728</v>
@@ -26000,7 +26003,7 @@
         <v>85</v>
       </c>
       <c r="S177" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="T177" t="s" s="2">
         <v>85</v>
@@ -26015,13 +26018,13 @@
         <v>85</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>85</v>
@@ -26054,7 +26057,7 @@
         <v>107</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>85</v>
@@ -26069,13 +26072,13 @@
         <v>733</v>
       </c>
       <c r="AP177" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ177" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS177" t="s" s="2">
         <v>85</v>
@@ -26083,7 +26086,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>734</v>
@@ -26146,7 +26149,7 @@
         <v>85</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y178" t="s" s="2">
         <v>493</v>
@@ -26158,7 +26161,7 @@
         <v>85</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
@@ -26212,13 +26215,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>734</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>85</v>
@@ -26277,7 +26280,7 @@
         <v>85</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y179" t="s" s="2">
         <v>493</v>
@@ -26345,7 +26348,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>787</v>
@@ -26371,7 +26374,7 @@
         <v>85</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L180" t="s" s="2">
         <v>154</v>
@@ -26472,14 +26475,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -26501,13 +26504,13 @@
         <v>140</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -26601,10 +26604,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26627,19 +26630,19 @@
         <v>96</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>85</v>
@@ -26668,7 +26671,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>85</v>
@@ -26686,7 +26689,7 @@
         <v>85</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>83</v>
@@ -26701,13 +26704,13 @@
         <v>107</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>85</v>
@@ -26716,10 +26719,10 @@
         <v>85</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>85</v>
@@ -26730,10 +26733,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26756,19 +26759,19 @@
         <v>96</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>85</v>
@@ -26817,7 +26820,7 @@
         <v>85</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>83</v>
@@ -26847,10 +26850,10 @@
         <v>85</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>85</v>
@@ -26861,7 +26864,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>740</v>
@@ -26924,7 +26927,7 @@
         <v>85</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y184" t="s" s="2">
         <v>588</v>
@@ -26992,7 +26995,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>746</v>
@@ -27055,7 +27058,7 @@
         <v>85</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y185" t="s" s="2">
         <v>599</v>
@@ -27123,7 +27126,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>747</v>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,7 +931,7 @@
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
-    <t>Observation.ObservationExtension.Removed</t>
+    <t>Observation.Extension[ObservationExtension].Removed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1283,7 +1283,7 @@
     <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
-    <t>Observation.ObservationCode,Observation.ObservationExtension.BMI</t>
+    <t>Observation.ObservationCode,Observation.Extension[ObservationExtension].BMI</t>
   </si>
   <si>
     <t>Observation.code.coding:PulseOx</t>
@@ -1467,7 +1467,7 @@
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>Observation.Observation.Description,Observation.ObservationMethod.Description</t>
+    <t>Observation.ObservationCode[Observation].Description,Observation.ObservationMethods[ObservationMethod].Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1523,7 +1523,7 @@
     <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
-    <t>Observation.EnteredAt,Observation.ObservationExtension.Location</t>
+    <t>Observation.EnteredAt,Observation.Extension[ObservationExtension].Location</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1632,7 +1632,7 @@
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
-    <t>Observation.ObservationValue,Observation.ObservationExtension.BMI</t>
+    <t>Observation.ObservationValue,Observation.Extension[ObservationExtension].BMI</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -2501,7 +2501,7 @@
     <t>Vital.VitalSign.SupplementalO2</t>
   </si>
   <si>
-    <t>Observation.ObservationExtension.SupplementalO2</t>
+    <t>Observation.Extension[ObservationExtension].SupplementalO2</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.value[x].comparator</t>
@@ -3152,7 +3152,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="76.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="114.0859375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-pulse-oximetry</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-pulse-oximetry.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$187</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7755" uniqueCount="890">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1818,7 +1818,7 @@
 </t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VitalsUnits</t>
+    <t>http://va.gov/fhir/ConceptMap/VF-VitalsUnits</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.value</t>
@@ -2328,6 +2328,12 @@
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>2193: target not supported</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -3112,7 +3118,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS186"/>
+  <dimension ref="A1:AS187"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -16154,16 +16160,14 @@
         <v>85</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC101" s="2"/>
       <c r="AD101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>734</v>
@@ -16213,9 +16217,11 @@
         <v>740</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>734</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="D102" t="s" s="2">
         <v>85</v>
       </c>
@@ -16233,22 +16239,22 @@
         <v>85</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>172</v>
+        <v>502</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>587</v>
+        <v>492</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -16276,10 +16282,10 @@
         <v>228</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>588</v>
+        <v>493</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>589</v>
+        <v>494</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -16297,7 +16303,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -16306,13 +16312,13 @@
         <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>85</v>
@@ -16324,41 +16330,41 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>85</v>
+        <v>739</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>138</v>
+        <v>497</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>592</v>
+        <v>498</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>85</v>
@@ -16370,16 +16376,16 @@
         <v>172</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>596</v>
+        <v>744</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>597</v>
+        <v>745</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
@@ -16407,10 +16413,10 @@
         <v>228</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>85</v>
@@ -16428,22 +16434,22 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>85</v>
+        <v>747</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>85</v>
@@ -16455,31 +16461,31 @@
         <v>85</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS103" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -16498,19 +16504,19 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>748</v>
+        <v>595</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>749</v>
+        <v>596</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
@@ -16535,13 +16541,13 @@
         <v>85</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>85</v>
@@ -16559,7 +16565,7 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16586,31 +16592,29 @@
         <v>85</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>85</v>
+        <v>601</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS104" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>751</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>85</v>
       </c>
@@ -16619,31 +16623,31 @@
         <v>83</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>651</v>
+        <v>86</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>719</v>
+        <v>654</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>720</v>
+        <v>655</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>85</v>
@@ -16692,7 +16696,7 @@
         <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
@@ -16704,7 +16708,7 @@
         <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>722</v>
+        <v>107</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>85</v>
@@ -16722,10 +16726,10 @@
         <v>85</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>724</v>
+        <v>658</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>85</v>
@@ -16736,12 +16740,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C106" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>753</v>
+      </c>
       <c r="D106" t="s" s="2">
         <v>85</v>
       </c>
@@ -16753,25 +16759,29 @@
         <v>95</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>210</v>
+        <v>651</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>154</v>
+        <v>754</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>755</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>85</v>
       </c>
@@ -16819,19 +16829,19 @@
         <v>85</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>156</v>
+        <v>717</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>85</v>
+        <v>722</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>85</v>
@@ -16849,10 +16859,10 @@
         <v>85</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>158</v>
+        <v>724</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>85</v>
@@ -16863,21 +16873,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>85</v>
@@ -16889,17 +16899,15 @@
         <v>85</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>85</v>
@@ -16948,19 +16956,19 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>85</v>
@@ -16992,14 +17000,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>662</v>
+        <v>194</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -17012,26 +17020,24 @@
         <v>85</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>664</v>
+        <v>213</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O108" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>85</v>
       </c>
@@ -17079,7 +17085,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>665</v>
+        <v>162</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -17112,7 +17118,7 @@
         <v>85</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>85</v>
@@ -17123,45 +17129,45 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>85</v>
+        <v>662</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I109" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>729</v>
+        <v>663</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>730</v>
+        <v>664</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>731</v>
+        <v>197</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>732</v>
+        <v>198</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>85</v>
@@ -17171,7 +17177,7 @@
         <v>85</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>758</v>
+        <v>85</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>85</v>
@@ -17186,13 +17192,13 @@
         <v>85</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>85</v>
@@ -17210,19 +17216,19 @@
         <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>728</v>
+        <v>665</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>85</v>
@@ -17237,16 +17243,16 @@
         <v>85</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="AS109" t="s" s="2">
         <v>85</v>
@@ -17257,7 +17263,7 @@
         <v>759</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>760</v>
+        <v>728</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17265,31 +17271,35 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>154</v>
+        <v>729</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>732</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
       </c>
@@ -17298,7 +17308,7 @@
         <v>85</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>85</v>
+        <v>760</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>85</v>
@@ -17313,13 +17323,13 @@
         <v>85</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>85</v>
+        <v>392</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>85</v>
@@ -17337,10 +17347,10 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>156</v>
+        <v>728</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>95</v>
@@ -17349,7 +17359,7 @@
         <v>85</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>85</v>
@@ -17364,16 +17374,16 @@
         <v>85</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>85</v>
+        <v>396</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>158</v>
+        <v>397</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AS110" t="s" s="2">
         <v>85</v>
@@ -17388,14 +17398,14 @@
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>85</v>
@@ -17407,17 +17417,15 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>85</v>
@@ -17454,31 +17462,31 @@
         <v>85</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>85</v>
@@ -17517,7 +17525,7 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -17533,23 +17541,21 @@
         <v>85</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>85</v>
       </c>
@@ -17585,19 +17591,19 @@
         <v>85</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -17609,7 +17615,7 @@
         <v>85</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>85</v>
@@ -17627,10 +17633,10 @@
         <v>85</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
@@ -17655,7 +17661,7 @@
         <v>83</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>85</v>
@@ -17664,19 +17670,23 @@
         <v>85</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>85</v>
       </c>
@@ -17724,19 +17734,19 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>156</v>
+        <v>325</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>85</v>
@@ -17754,10 +17764,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17775,14 +17785,14 @@
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>85</v>
@@ -17794,17 +17804,15 @@
         <v>85</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>85</v>
@@ -17841,31 +17849,31 @@
         <v>85</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>85</v>
@@ -17904,39 +17912,37 @@
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>335</v>
+        <v>213</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>85</v>
       </c>
@@ -17972,34 +17978,34 @@
         <v>85</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>339</v>
+        <v>162</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>771</v>
+        <v>146</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>772</v>
+        <v>85</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>85</v>
@@ -18014,10 +18020,10 @@
         <v>85</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>341</v>
+        <v>158</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>85</v>
@@ -18028,10 +18034,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18045,7 +18051,7 @@
         <v>95</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>85</v>
@@ -18054,18 +18060,20 @@
         <v>96</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>85</v>
       </c>
@@ -18113,7 +18121,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -18125,10 +18133,10 @@
         <v>85</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>107</v>
+        <v>773</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>85</v>
+        <v>774</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>85</v>
@@ -18143,10 +18151,10 @@
         <v>85</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
@@ -18174,7 +18182,7 @@
         <v>95</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>85</v>
@@ -18183,18 +18191,18 @@
         <v>96</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>85</v>
       </c>
@@ -18242,7 +18250,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -18254,10 +18262,10 @@
         <v>85</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>777</v>
+        <v>107</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>778</v>
+        <v>85</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>85</v>
@@ -18272,10 +18280,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -18286,10 +18294,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18303,7 +18311,7 @@
         <v>95</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>85</v>
@@ -18312,17 +18320,17 @@
         <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
@@ -18371,7 +18379,7 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -18383,10 +18391,10 @@
         <v>85</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>107</v>
+        <v>779</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>85</v>
+        <v>780</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>85</v>
@@ -18401,10 +18409,10 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
@@ -18441,19 +18449,17 @@
         <v>96</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>85</v>
@@ -18502,7 +18508,7 @@
         <v>85</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -18532,10 +18538,10 @@
         <v>85</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>85</v>
@@ -18572,19 +18578,19 @@
         <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>210</v>
+        <v>369</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>85</v>
@@ -18633,7 +18639,7 @@
         <v>85</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
@@ -18663,10 +18669,10 @@
         <v>85</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>85</v>
@@ -18680,7 +18686,7 @@
         <v>785</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>734</v>
+        <v>786</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18694,7 +18700,7 @@
         <v>95</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>85</v>
@@ -18703,19 +18709,19 @@
         <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>502</v>
+        <v>210</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>735</v>
+        <v>379</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>736</v>
+        <v>380</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>737</v>
+        <v>381</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>492</v>
+        <v>382</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>85</v>
@@ -18740,13 +18746,13 @@
         <v>85</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>493</v>
+        <v>85</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>85</v>
@@ -18764,7 +18770,7 @@
         <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>734</v>
+        <v>383</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
@@ -18773,7 +18779,7 @@
         <v>95</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>738</v>
+        <v>85</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>107</v>
@@ -18791,27 +18797,27 @@
         <v>85</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>497</v>
+        <v>384</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>498</v>
+        <v>385</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS121" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>787</v>
+        <v>734</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18825,25 +18831,29 @@
         <v>95</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>210</v>
+        <v>502</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>154</v>
+        <v>735</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>85</v>
       </c>
@@ -18867,13 +18877,13 @@
         <v>85</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>85</v>
@@ -18891,7 +18901,7 @@
         <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>156</v>
+        <v>734</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -18900,10 +18910,10 @@
         <v>95</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>85</v>
+        <v>738</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>85</v>
@@ -18918,19 +18928,19 @@
         <v>85</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>85</v>
+        <v>739</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>158</v>
+        <v>498</v>
       </c>
       <c r="AR122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS122" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
     </row>
     <row r="123" hidden="true">
@@ -18942,14 +18952,14 @@
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>85</v>
@@ -18961,17 +18971,15 @@
         <v>85</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>85</v>
@@ -19008,31 +19016,31 @@
         <v>85</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>85</v>
@@ -19071,39 +19079,37 @@
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>509</v>
+        <v>140</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>510</v>
+        <v>212</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>511</v>
+        <v>213</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>85</v>
       </c>
@@ -19139,40 +19145,40 @@
         <v>85</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>514</v>
+        <v>162</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>792</v>
+        <v>85</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>793</v>
+        <v>85</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>794</v>
+        <v>85</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>85</v>
@@ -19181,10 +19187,10 @@
         <v>85</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>519</v>
+        <v>158</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>85</v>
@@ -19195,10 +19201,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19206,39 +19212,39 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>115</v>
+        <v>509</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="O125" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q125" t="s" s="2">
-        <v>525</v>
-      </c>
+      <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
         <v>85</v>
       </c>
@@ -19258,13 +19264,13 @@
         <v>85</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>527</v>
+        <v>85</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>85</v>
@@ -19282,7 +19288,7 @@
         <v>85</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>83</v>
@@ -19297,13 +19303,13 @@
         <v>107</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>85</v>
+        <v>794</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>85</v>
+        <v>795</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>85</v>
+        <v>796</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>85</v>
@@ -19312,10 +19318,10 @@
         <v>85</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>85</v>
@@ -19337,37 +19343,39 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H126" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I126" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q126" s="2"/>
+      <c r="Q126" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="R126" t="s" s="2">
         <v>85</v>
       </c>
@@ -19387,13 +19395,13 @@
         <v>85</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>85</v>
@@ -19411,7 +19419,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19441,10 +19449,10 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19481,24 +19489,24 @@
         <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>801</v>
+        <v>85</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>85</v>
@@ -19540,7 +19548,7 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -19549,7 +19557,7 @@
         <v>95</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>107</v>
@@ -19573,7 +19581,7 @@
         <v>537</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
@@ -19584,10 +19592,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19610,26 +19618,24 @@
         <v>96</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>85</v>
@@ -19671,7 +19677,7 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -19680,13 +19686,13 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>85</v>
+        <v>545</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>805</v>
+        <v>107</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>806</v>
+        <v>85</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>85</v>
@@ -19704,7 +19710,7 @@
         <v>537</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
@@ -19715,10 +19721,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>740</v>
+        <v>805</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19726,7 +19732,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>95</v>
@@ -19738,29 +19744,29 @@
         <v>85</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>741</v>
+        <v>549</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>742</v>
+        <v>550</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>743</v>
+        <v>551</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>587</v>
+        <v>552</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>85</v>
+        <v>806</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>85</v>
@@ -19778,13 +19784,13 @@
         <v>85</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>588</v>
+        <v>85</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>589</v>
+        <v>85</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>85</v>
@@ -19802,7 +19808,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>740</v>
+        <v>553</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19811,13 +19817,13 @@
         <v>95</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>744</v>
+        <v>85</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>107</v>
+        <v>807</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>85</v>
+        <v>808</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>85</v>
@@ -19832,10 +19838,10 @@
         <v>85</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>138</v>
+        <v>537</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
@@ -19846,24 +19852,24 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>85</v>
@@ -19875,16 +19881,16 @@
         <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>596</v>
+        <v>744</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>597</v>
+        <v>745</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>85</v>
@@ -19912,10 +19918,10 @@
         <v>228</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>85</v>
@@ -19933,16 +19939,16 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI130" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>107</v>
@@ -19960,31 +19966,31 @@
         <v>85</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS130" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -20003,19 +20009,19 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>748</v>
+        <v>595</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>749</v>
+        <v>596</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>85</v>
@@ -20040,13 +20046,13 @@
         <v>85</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>85</v>
@@ -20064,7 +20070,7 @@
         <v>85</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
@@ -20091,31 +20097,29 @@
         <v>85</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>85</v>
+        <v>601</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS131" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>811</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>85</v>
       </c>
@@ -20124,31 +20128,31 @@
         <v>83</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>651</v>
+        <v>86</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>812</v>
+        <v>750</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>719</v>
+        <v>654</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>720</v>
+        <v>655</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>85</v>
@@ -20197,7 +20201,7 @@
         <v>85</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>83</v>
@@ -20209,7 +20213,7 @@
         <v>85</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>722</v>
+        <v>107</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>85</v>
@@ -20227,10 +20231,10 @@
         <v>85</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>724</v>
+        <v>658</v>
       </c>
       <c r="AR132" t="s" s="2">
         <v>85</v>
@@ -20241,12 +20245,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C133" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="B133" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>85</v>
       </c>
@@ -20258,25 +20264,29 @@
         <v>95</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>210</v>
+        <v>651</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>154</v>
+        <v>814</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>755</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>85</v>
       </c>
@@ -20324,19 +20334,19 @@
         <v>85</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>156</v>
+        <v>717</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>85</v>
+        <v>722</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>85</v>
@@ -20354,10 +20364,10 @@
         <v>85</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>158</v>
+        <v>724</v>
       </c>
       <c r="AR133" t="s" s="2">
         <v>85</v>
@@ -20368,21 +20378,21 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>85</v>
@@ -20394,17 +20404,15 @@
         <v>85</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>85</v>
@@ -20453,19 +20461,19 @@
         <v>85</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>85</v>
@@ -20497,14 +20505,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>662</v>
+        <v>194</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -20517,26 +20525,24 @@
         <v>85</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>664</v>
+        <v>213</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O135" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>85</v>
       </c>
@@ -20584,7 +20590,7 @@
         <v>85</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>665</v>
+        <v>162</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>83</v>
@@ -20617,7 +20623,7 @@
         <v>85</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR135" t="s" s="2">
         <v>85</v>
@@ -20628,45 +20634,45 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>85</v>
+        <v>662</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H136" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I136" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J136" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>729</v>
+        <v>663</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>730</v>
+        <v>664</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>731</v>
+        <v>197</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>732</v>
+        <v>198</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>85</v>
@@ -20676,7 +20682,7 @@
         <v>85</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>817</v>
+        <v>85</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>85</v>
@@ -20691,13 +20697,13 @@
         <v>85</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>85</v>
@@ -20715,19 +20721,19 @@
         <v>85</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>728</v>
+        <v>665</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>85</v>
@@ -20742,16 +20748,16 @@
         <v>85</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="AR136" t="s" s="2">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="AS136" t="s" s="2">
         <v>85</v>
@@ -20762,7 +20768,7 @@
         <v>818</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>760</v>
+        <v>728</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20770,31 +20776,35 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>154</v>
+        <v>729</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>732</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>85</v>
       </c>
@@ -20803,7 +20813,7 @@
         <v>85</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>85</v>
+        <v>819</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>85</v>
@@ -20818,13 +20828,13 @@
         <v>85</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>85</v>
+        <v>392</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>85</v>
@@ -20842,10 +20852,10 @@
         <v>85</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>156</v>
+        <v>728</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>95</v>
@@ -20854,7 +20864,7 @@
         <v>85</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>85</v>
@@ -20869,16 +20879,16 @@
         <v>85</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>85</v>
+        <v>396</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>158</v>
+        <v>397</v>
       </c>
       <c r="AR137" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AS137" t="s" s="2">
         <v>85</v>
@@ -20886,21 +20896,21 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>762</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>85</v>
@@ -20912,17 +20922,15 @@
         <v>85</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>85</v>
@@ -20959,31 +20967,31 @@
         <v>85</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>85</v>
@@ -21015,14 +21023,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>764</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -21038,23 +21046,21 @@
         <v>85</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>85</v>
       </c>
@@ -21090,19 +21096,19 @@
         <v>85</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>83</v>
@@ -21114,7 +21120,7 @@
         <v>85</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>85</v>
@@ -21132,10 +21138,10 @@
         <v>85</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>85</v>
@@ -21146,7 +21152,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>766</v>
@@ -21160,7 +21166,7 @@
         <v>83</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>85</v>
@@ -21169,19 +21175,23 @@
         <v>85</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>85</v>
       </c>
@@ -21229,19 +21239,19 @@
         <v>85</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>156</v>
+        <v>325</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>85</v>
@@ -21259,10 +21269,10 @@
         <v>85</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>85</v>
@@ -21273,21 +21283,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>768</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>85</v>
@@ -21299,17 +21309,15 @@
         <v>85</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>85</v>
@@ -21346,31 +21354,31 @@
         <v>85</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>85</v>
@@ -21402,46 +21410,44 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>770</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>335</v>
+        <v>213</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>85</v>
       </c>
@@ -21477,34 +21483,34 @@
         <v>85</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>339</v>
+        <v>162</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>824</v>
+        <v>146</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>825</v>
+        <v>85</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>85</v>
@@ -21519,10 +21525,10 @@
         <v>85</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>341</v>
+        <v>158</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>85</v>
@@ -21533,10 +21539,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21550,7 +21556,7 @@
         <v>95</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>85</v>
@@ -21559,18 +21565,20 @@
         <v>96</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O143" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>85</v>
       </c>
@@ -21618,7 +21626,7 @@
         <v>85</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>83</v>
@@ -21630,10 +21638,10 @@
         <v>85</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>107</v>
+        <v>826</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>85</v>
+        <v>827</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>85</v>
@@ -21648,10 +21656,10 @@
         <v>85</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>85</v>
@@ -21662,7 +21670,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>776</v>
@@ -21679,7 +21687,7 @@
         <v>95</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>85</v>
@@ -21688,18 +21696,18 @@
         <v>96</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>85</v>
       </c>
@@ -21747,7 +21755,7 @@
         <v>85</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>83</v>
@@ -21759,10 +21767,10 @@
         <v>85</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>828</v>
+        <v>107</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>829</v>
+        <v>85</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>85</v>
@@ -21777,10 +21785,10 @@
         <v>85</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>85</v>
@@ -21791,10 +21799,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21808,7 +21816,7 @@
         <v>95</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>85</v>
@@ -21817,17 +21825,17 @@
         <v>96</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>85</v>
@@ -21876,7 +21884,7 @@
         <v>85</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>83</v>
@@ -21888,10 +21896,10 @@
         <v>85</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>107</v>
+        <v>830</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>85</v>
+        <v>831</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>85</v>
@@ -21906,10 +21914,10 @@
         <v>85</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>85</v>
@@ -21920,7 +21928,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>782</v>
@@ -21946,19 +21954,17 @@
         <v>96</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>85</v>
@@ -22007,7 +22013,7 @@
         <v>85</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>83</v>
@@ -22037,10 +22043,10 @@
         <v>85</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>85</v>
@@ -22051,7 +22057,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>784</v>
@@ -22077,19 +22083,19 @@
         <v>96</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>210</v>
+        <v>369</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>85</v>
@@ -22138,7 +22144,7 @@
         <v>85</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>83</v>
@@ -22168,10 +22174,10 @@
         <v>85</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>85</v>
@@ -22182,10 +22188,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>734</v>
+        <v>786</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22199,7 +22205,7 @@
         <v>95</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>85</v>
@@ -22208,19 +22214,19 @@
         <v>96</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>502</v>
+        <v>210</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>735</v>
+        <v>379</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>736</v>
+        <v>380</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>737</v>
+        <v>381</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>492</v>
+        <v>382</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>85</v>
@@ -22245,13 +22251,13 @@
         <v>85</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>493</v>
+        <v>85</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>85</v>
@@ -22269,7 +22275,7 @@
         <v>85</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>734</v>
+        <v>383</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>83</v>
@@ -22278,7 +22284,7 @@
         <v>95</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>738</v>
+        <v>85</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>107</v>
@@ -22296,27 +22302,27 @@
         <v>85</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>497</v>
+        <v>384</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>498</v>
+        <v>385</v>
       </c>
       <c r="AR148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS148" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>787</v>
+        <v>734</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22330,25 +22336,29 @@
         <v>95</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>210</v>
+        <v>502</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>154</v>
+        <v>735</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>85</v>
       </c>
@@ -22372,13 +22382,13 @@
         <v>85</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>85</v>
@@ -22396,7 +22406,7 @@
         <v>85</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>156</v>
+        <v>734</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>83</v>
@@ -22405,10 +22415,10 @@
         <v>95</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>85</v>
+        <v>738</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>85</v>
@@ -22423,38 +22433,38 @@
         <v>85</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>85</v>
+        <v>739</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>158</v>
+        <v>498</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS149" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>85</v>
@@ -22466,17 +22476,15 @@
         <v>85</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>85</v>
@@ -22513,31 +22521,31 @@
         <v>85</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>85</v>
@@ -22569,46 +22577,44 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>791</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>509</v>
+        <v>140</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>510</v>
+        <v>212</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>511</v>
+        <v>213</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>85</v>
       </c>
@@ -22644,40 +22650,40 @@
         <v>85</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>514</v>
+        <v>162</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>837</v>
+        <v>85</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>793</v>
+        <v>85</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>794</v>
+        <v>85</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>85</v>
@@ -22686,10 +22692,10 @@
         <v>85</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>519</v>
+        <v>158</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>85</v>
@@ -22703,7 +22709,7 @@
         <v>838</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22711,39 +22717,39 @@
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J152" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>115</v>
+        <v>509</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="O152" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q152" t="s" s="2">
-        <v>525</v>
-      </c>
+      <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
         <v>85</v>
       </c>
@@ -22763,13 +22769,13 @@
         <v>85</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>527</v>
+        <v>85</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>85</v>
@@ -22787,7 +22793,7 @@
         <v>85</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>83</v>
@@ -22802,13 +22808,13 @@
         <v>107</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>85</v>
+        <v>839</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>85</v>
+        <v>795</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>85</v>
+        <v>796</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>85</v>
@@ -22817,10 +22823,10 @@
         <v>85</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>85</v>
@@ -22831,7 +22837,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>798</v>
@@ -22842,37 +22848,39 @@
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G153" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H153" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I153" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J153" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q153" s="2"/>
+      <c r="Q153" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="R153" t="s" s="2">
         <v>85</v>
       </c>
@@ -22892,13 +22900,13 @@
         <v>85</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>85</v>
@@ -22916,7 +22924,7 @@
         <v>85</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>83</v>
@@ -22946,10 +22954,10 @@
         <v>85</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>85</v>
@@ -22960,7 +22968,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>800</v>
@@ -22986,24 +22994,24 @@
         <v>96</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>801</v>
+        <v>85</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>85</v>
@@ -23045,7 +23053,7 @@
         <v>85</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>83</v>
@@ -23054,7 +23062,7 @@
         <v>95</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>107</v>
@@ -23078,7 +23086,7 @@
         <v>537</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>85</v>
@@ -23089,10 +23097,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23115,26 +23123,24 @@
         <v>96</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>842</v>
+        <v>803</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>85</v>
@@ -23176,7 +23182,7 @@
         <v>85</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>83</v>
@@ -23185,13 +23191,13 @@
         <v>95</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>85</v>
+        <v>545</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>843</v>
+        <v>107</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>844</v>
+        <v>85</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>85</v>
@@ -23209,7 +23215,7 @@
         <v>537</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>85</v>
@@ -23220,10 +23226,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>740</v>
+        <v>805</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -23231,7 +23237,7 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>95</v>
@@ -23243,29 +23249,29 @@
         <v>85</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>741</v>
+        <v>549</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>742</v>
+        <v>550</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>743</v>
+        <v>551</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>587</v>
+        <v>552</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
-        <v>85</v>
+        <v>844</v>
       </c>
       <c r="S156" t="s" s="2">
         <v>85</v>
@@ -23283,13 +23289,13 @@
         <v>85</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>588</v>
+        <v>85</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>589</v>
+        <v>85</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>85</v>
@@ -23307,7 +23313,7 @@
         <v>85</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>740</v>
+        <v>553</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>83</v>
@@ -23316,13 +23322,13 @@
         <v>95</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>744</v>
+        <v>85</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>107</v>
+        <v>845</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>85</v>
+        <v>846</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>85</v>
@@ -23337,10 +23343,10 @@
         <v>85</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>138</v>
+        <v>537</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>85</v>
@@ -23351,24 +23357,24 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>85</v>
@@ -23380,16 +23386,16 @@
         <v>172</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>596</v>
+        <v>744</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>597</v>
+        <v>745</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>85</v>
@@ -23417,10 +23423,10 @@
         <v>228</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>85</v>
@@ -23438,16 +23444,16 @@
         <v>85</v>
       </c>
       <c r="AF157" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI157" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>107</v>
@@ -23465,31 +23471,31 @@
         <v>85</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS157" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -23508,19 +23514,19 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>748</v>
+        <v>595</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>749</v>
+        <v>596</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>85</v>
@@ -23545,13 +23551,13 @@
         <v>85</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>85</v>
@@ -23569,7 +23575,7 @@
         <v>85</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>83</v>
@@ -23596,31 +23602,29 @@
         <v>85</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>85</v>
+        <v>601</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS158" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>849</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>85</v>
       </c>
@@ -23629,31 +23633,31 @@
         <v>83</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>651</v>
+        <v>86</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>718</v>
+        <v>751</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>719</v>
+        <v>654</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>720</v>
+        <v>655</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>85</v>
@@ -23702,7 +23706,7 @@
         <v>85</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>83</v>
@@ -23714,7 +23718,7 @@
         <v>85</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>722</v>
+        <v>107</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>85</v>
@@ -23732,10 +23736,10 @@
         <v>85</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>724</v>
+        <v>658</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>85</v>
@@ -23749,9 +23753,11 @@
         <v>850</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C160" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>851</v>
+      </c>
       <c r="D160" t="s" s="2">
         <v>85</v>
       </c>
@@ -23763,25 +23769,29 @@
         <v>95</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>210</v>
+        <v>651</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>154</v>
+        <v>718</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>718</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>85</v>
       </c>
@@ -23829,19 +23839,19 @@
         <v>85</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>156</v>
+        <v>717</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>85</v>
+        <v>722</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>85</v>
@@ -23859,10 +23869,10 @@
         <v>85</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>158</v>
+        <v>724</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>85</v>
@@ -23873,21 +23883,21 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>85</v>
@@ -23899,17 +23909,15 @@
         <v>85</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>85</v>
@@ -23958,19 +23966,19 @@
         <v>85</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>85</v>
@@ -24002,14 +24010,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>662</v>
+        <v>194</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -24022,26 +24030,24 @@
         <v>85</v>
       </c>
       <c r="I162" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K162" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>664</v>
+        <v>213</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O162" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>85</v>
       </c>
@@ -24089,7 +24095,7 @@
         <v>85</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>665</v>
+        <v>162</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>83</v>
@@ -24122,7 +24128,7 @@
         <v>85</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>85</v>
@@ -24133,45 +24139,45 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>85</v>
+        <v>662</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H163" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I163" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I163" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J163" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>729</v>
+        <v>663</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>730</v>
+        <v>664</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>731</v>
+        <v>197</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>732</v>
+        <v>198</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>85</v>
@@ -24181,7 +24187,7 @@
         <v>85</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>854</v>
+        <v>85</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>85</v>
@@ -24196,13 +24202,13 @@
         <v>85</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>85</v>
@@ -24220,22 +24226,22 @@
         <v>85</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>728</v>
+        <v>665</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>855</v>
+        <v>85</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>85</v>
@@ -24247,16 +24253,16 @@
         <v>85</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="AR163" t="s" s="2">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="AS163" t="s" s="2">
         <v>85</v>
@@ -24264,10 +24270,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24275,7 +24281,7 @@
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G164" t="s" s="2">
         <v>95</v>
@@ -24290,19 +24296,19 @@
         <v>96</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>488</v>
+        <v>172</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>492</v>
+        <v>732</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>85</v>
@@ -24312,7 +24318,7 @@
         <v>85</v>
       </c>
       <c r="S164" t="s" s="2">
-        <v>85</v>
+        <v>856</v>
       </c>
       <c r="T164" t="s" s="2">
         <v>85</v>
@@ -24330,41 +24336,43 @@
         <v>228</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>493</v>
+        <v>392</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC164" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD164" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>738</v>
+        <v>85</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>85</v>
+        <v>857</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>85</v>
@@ -24376,31 +24384,29 @@
         <v>85</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>497</v>
+        <v>396</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>498</v>
+        <v>397</v>
       </c>
       <c r="AR164" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AS164" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="C165" t="s" s="2">
-        <v>858</v>
-      </c>
+      <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>85</v>
       </c>
@@ -24421,7 +24427,7 @@
         <v>96</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>172</v>
+        <v>488</v>
       </c>
       <c r="L165" t="s" s="2">
         <v>735</v>
@@ -24470,16 +24476,14 @@
         <v>85</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC165" s="2"/>
       <c r="AD165" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF165" t="s" s="2">
         <v>734</v>
@@ -24529,9 +24533,11 @@
         <v>859</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C166" s="2"/>
+        <v>734</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>860</v>
+      </c>
       <c r="D166" t="s" s="2">
         <v>85</v>
       </c>
@@ -24543,25 +24549,29 @@
         <v>95</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>154</v>
+        <v>735</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P166" t="s" s="2">
         <v>85</v>
       </c>
@@ -24585,13 +24595,13 @@
         <v>85</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>85</v>
@@ -24609,7 +24619,7 @@
         <v>85</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>156</v>
+        <v>734</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>83</v>
@@ -24618,10 +24628,10 @@
         <v>95</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>85</v>
+        <v>738</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>85</v>
@@ -24636,38 +24646,38 @@
         <v>85</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>85</v>
+        <v>739</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>158</v>
+        <v>498</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS166" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>85</v>
@@ -24679,17 +24689,15 @@
         <v>85</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>85</v>
@@ -24726,31 +24734,31 @@
         <v>85</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>85</v>
@@ -24782,14 +24790,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>862</v>
+        <v>791</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -24799,29 +24807,27 @@
         <v>84</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>85</v>
       </c>
@@ -24845,29 +24851,31 @@
         <v>85</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y168" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z168" t="s" s="2">
-        <v>863</v>
+        <v>85</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>83</v>
@@ -24879,16 +24887,16 @@
         <v>85</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>864</v>
+        <v>85</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>85</v>
@@ -24897,10 +24905,10 @@
         <v>85</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>85</v>
@@ -24911,10 +24919,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24925,10 +24933,10 @@
         <v>83</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>85</v>
@@ -24937,19 +24945,19 @@
         <v>96</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>85</v>
@@ -24974,13 +24982,11 @@
         <v>85</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>85</v>
+        <v>865</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>85</v>
@@ -24998,13 +25004,13 @@
         <v>85</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>85</v>
@@ -25013,13 +25019,13 @@
         <v>107</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>85</v>
+        <v>866</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>85</v>
@@ -25028,10 +25034,10 @@
         <v>85</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ169" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR169" t="s" s="2">
         <v>85</v>
@@ -25045,7 +25051,7 @@
         <v>867</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>740</v>
+        <v>868</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -25059,28 +25065,28 @@
         <v>95</v>
       </c>
       <c r="H170" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J170" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I170" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K170" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>741</v>
+        <v>379</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>742</v>
+        <v>380</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>743</v>
+        <v>381</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>587</v>
+        <v>382</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>85</v>
@@ -25105,13 +25111,13 @@
         <v>85</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>588</v>
+        <v>85</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>589</v>
+        <v>85</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>85</v>
@@ -25129,7 +25135,7 @@
         <v>85</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>740</v>
+        <v>383</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -25138,7 +25144,7 @@
         <v>95</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>744</v>
+        <v>85</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>107</v>
@@ -25159,10 +25165,10 @@
         <v>85</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ170" t="s" s="2">
-        <v>592</v>
+        <v>385</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>85</v>
@@ -25173,24 +25179,24 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>85</v>
@@ -25202,16 +25208,16 @@
         <v>172</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>596</v>
+        <v>744</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>597</v>
+        <v>745</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>85</v>
@@ -25239,10 +25245,10 @@
         <v>228</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>85</v>
@@ -25260,16 +25266,16 @@
         <v>85</v>
       </c>
       <c r="AF171" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI171" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>107</v>
@@ -25287,31 +25293,31 @@
         <v>85</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS171" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -25330,19 +25336,19 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>748</v>
+        <v>595</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>749</v>
+        <v>596</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>85</v>
@@ -25367,13 +25373,13 @@
         <v>85</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>85</v>
@@ -25391,7 +25397,7 @@
         <v>85</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
@@ -25418,31 +25424,29 @@
         <v>85</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>85</v>
+        <v>601</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS172" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>871</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
         <v>85</v>
       </c>
@@ -25451,31 +25455,31 @@
         <v>83</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>651</v>
+        <v>86</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>718</v>
+        <v>751</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>719</v>
+        <v>654</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>720</v>
+        <v>655</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>85</v>
@@ -25524,7 +25528,7 @@
         <v>85</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>83</v>
@@ -25536,7 +25540,7 @@
         <v>85</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>722</v>
+        <v>107</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>85</v>
@@ -25554,10 +25558,10 @@
         <v>85</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>724</v>
+        <v>658</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>85</v>
@@ -25571,9 +25575,11 @@
         <v>872</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C174" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>873</v>
+      </c>
       <c r="D174" t="s" s="2">
         <v>85</v>
       </c>
@@ -25585,25 +25591,29 @@
         <v>95</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>210</v>
+        <v>651</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>154</v>
+        <v>718</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+        <v>718</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>85</v>
       </c>
@@ -25651,19 +25661,19 @@
         <v>85</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>156</v>
+        <v>717</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>85</v>
+        <v>722</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>85</v>
@@ -25681,10 +25691,10 @@
         <v>85</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>158</v>
+        <v>724</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>85</v>
@@ -25695,21 +25705,21 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>85</v>
@@ -25721,17 +25731,15 @@
         <v>85</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>85</v>
@@ -25780,19 +25788,19 @@
         <v>85</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>85</v>
@@ -25824,14 +25832,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>662</v>
+        <v>194</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -25844,26 +25852,24 @@
         <v>85</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K176" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>664</v>
+        <v>213</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O176" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>85</v>
       </c>
@@ -25911,7 +25917,7 @@
         <v>85</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>665</v>
+        <v>162</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>83</v>
@@ -25944,7 +25950,7 @@
         <v>85</v>
       </c>
       <c r="AQ176" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR176" t="s" s="2">
         <v>85</v>
@@ -25955,45 +25961,45 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>85</v>
+        <v>662</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H177" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I177" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J177" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>729</v>
+        <v>663</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>730</v>
+        <v>664</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>731</v>
+        <v>197</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>732</v>
+        <v>198</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>85</v>
@@ -26003,7 +26009,7 @@
         <v>85</v>
       </c>
       <c r="S177" t="s" s="2">
-        <v>854</v>
+        <v>85</v>
       </c>
       <c r="T177" t="s" s="2">
         <v>85</v>
@@ -26018,13 +26024,13 @@
         <v>85</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>85</v>
@@ -26042,22 +26048,22 @@
         <v>85</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>728</v>
+        <v>665</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>876</v>
+        <v>85</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>85</v>
@@ -26069,16 +26075,16 @@
         <v>85</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AP177" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="AQ177" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="AR177" t="s" s="2">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="AS177" t="s" s="2">
         <v>85</v>
@@ -26089,7 +26095,7 @@
         <v>877</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26097,7 +26103,7 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G178" t="s" s="2">
         <v>95</v>
@@ -26112,19 +26118,19 @@
         <v>96</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>488</v>
+        <v>172</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>492</v>
+        <v>732</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>85</v>
@@ -26134,7 +26140,7 @@
         <v>85</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>85</v>
+        <v>856</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>85</v>
@@ -26152,41 +26158,43 @@
         <v>228</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>493</v>
+        <v>392</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC178" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD178" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>738</v>
+        <v>85</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>85</v>
+        <v>878</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>85</v>
@@ -26198,31 +26206,29 @@
         <v>85</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="AP178" t="s" s="2">
-        <v>497</v>
+        <v>396</v>
       </c>
       <c r="AQ178" t="s" s="2">
-        <v>498</v>
+        <v>397</v>
       </c>
       <c r="AR178" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AS178" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="C179" t="s" s="2">
-        <v>858</v>
-      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>85</v>
       </c>
@@ -26243,7 +26249,7 @@
         <v>96</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>172</v>
+        <v>488</v>
       </c>
       <c r="L179" t="s" s="2">
         <v>735</v>
@@ -26292,16 +26298,14 @@
         <v>85</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC179" s="2"/>
       <c r="AD179" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF179" t="s" s="2">
         <v>734</v>
@@ -26348,12 +26352,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="C180" s="2"/>
+        <v>734</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>860</v>
+      </c>
       <c r="D180" t="s" s="2">
         <v>85</v>
       </c>
@@ -26365,25 +26371,29 @@
         <v>95</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>154</v>
+        <v>735</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>85</v>
       </c>
@@ -26407,13 +26417,13 @@
         <v>85</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>85</v>
@@ -26431,7 +26441,7 @@
         <v>85</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>156</v>
+        <v>734</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>83</v>
@@ -26440,10 +26450,10 @@
         <v>95</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>85</v>
+        <v>738</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>85</v>
@@ -26458,38 +26468,38 @@
         <v>85</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>85</v>
+        <v>739</v>
       </c>
       <c r="AP180" t="s" s="2">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>158</v>
+        <v>498</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS180" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>789</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>85</v>
@@ -26501,17 +26511,15 @@
         <v>85</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>85</v>
@@ -26548,31 +26556,31 @@
         <v>85</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>85</v>
@@ -26604,14 +26612,14 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>862</v>
+        <v>791</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -26621,29 +26629,27 @@
         <v>84</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>85</v>
       </c>
@@ -26667,29 +26673,31 @@
         <v>85</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y182" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z182" t="s" s="2">
-        <v>882</v>
+        <v>85</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>83</v>
@@ -26701,16 +26709,16 @@
         <v>85</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>883</v>
+        <v>85</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>85</v>
@@ -26719,10 +26727,10 @@
         <v>85</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>85</v>
@@ -26733,10 +26741,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26747,10 +26755,10 @@
         <v>83</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>85</v>
@@ -26759,19 +26767,19 @@
         <v>96</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>85</v>
@@ -26796,13 +26804,11 @@
         <v>85</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>85</v>
+        <v>884</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>85</v>
@@ -26820,13 +26826,13 @@
         <v>85</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>85</v>
@@ -26835,13 +26841,13 @@
         <v>107</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>85</v>
+        <v>885</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>85</v>
@@ -26850,10 +26856,10 @@
         <v>85</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>85</v>
@@ -26864,10 +26870,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>740</v>
+        <v>868</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26881,28 +26887,28 @@
         <v>95</v>
       </c>
       <c r="H184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J184" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I184" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K184" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>741</v>
+        <v>379</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>742</v>
+        <v>380</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>743</v>
+        <v>381</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>587</v>
+        <v>382</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>85</v>
@@ -26927,13 +26933,13 @@
         <v>85</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>588</v>
+        <v>85</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>589</v>
+        <v>85</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>85</v>
@@ -26951,7 +26957,7 @@
         <v>85</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>740</v>
+        <v>383</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>83</v>
@@ -26960,7 +26966,7 @@
         <v>95</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>744</v>
+        <v>85</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>107</v>
@@ -26981,10 +26987,10 @@
         <v>85</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>592</v>
+        <v>385</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>85</v>
@@ -26995,24 +27001,24 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>85</v>
@@ -27024,16 +27030,16 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>595</v>
+        <v>743</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>596</v>
+        <v>744</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>597</v>
+        <v>745</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>85</v>
@@ -27061,10 +27067,10 @@
         <v>228</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>85</v>
@@ -27082,16 +27088,16 @@
         <v>85</v>
       </c>
       <c r="AF185" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI185" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>107</v>
@@ -27109,31 +27115,31 @@
         <v>85</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>602</v>
+        <v>138</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS185" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -27152,19 +27158,19 @@
         <v>85</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>748</v>
+        <v>595</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>749</v>
+        <v>596</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>85</v>
@@ -27189,13 +27195,13 @@
         <v>85</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>85</v>
@@ -27213,7 +27219,7 @@
         <v>85</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>83</v>
@@ -27240,23 +27246,154 @@
         <v>85</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>85</v>
+        <v>601</v>
       </c>
       <c r="AP186" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AQ186" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AR186" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS186" t="s" s="2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="187" hidden="true">
+      <c r="A187" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP187" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AQ186" t="s" s="2">
+      <c r="AQ187" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AR186" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS186" t="s" s="2">
+      <c r="AR187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS187" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS186">
+  <autoFilter ref="A1:AS187">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27266,7 +27403,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI185">
+  <conditionalFormatting sqref="A2:AI186">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7755" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7755" uniqueCount="893">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -792,7 +792,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
+    <t>660: source value based on GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -925,10 +925,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-655:120.5-4: if null then #final {null}vsso-14-656:120.5-4: if not null then #entered-in-error {null}</t>
-  </si>
-  <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
+vsso-14-655:If (120.5-4) is null then fixed value #final {null}vsso-14-656:If (120.5-4) is not null then fixed value #entered-in-error {null}</t>
+  </si>
+  <si>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) if not null</t>
   </si>
   <si>
     <t>Observation.Extension[ObservationExtension].Removed</t>
@@ -1332,7 +1332,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
+    <t>659: reference based on GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Vital.VitalSign.PatientIEN</t>
@@ -1461,7 +1461,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
+    <t>657: source value based on GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1486,7 +1486,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
+    <t>652: source value based on GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1517,7 +1517,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+    <t>1653: reference based on GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Vital.VitalSign.LocationIEN</t>
@@ -1626,7 +1626,11 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsso-14-664:If VUID not = 4500634 then source value from (120.5-1.2) {null}</t>
+  </si>
+  <si>
+    <t>664: source value based on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) if VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -2437,10 +2441,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1239-2:undefined: if VUID = 4500637 then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>1239-2: fixed value = http://loinc.org case VUID = 4500637</t>
+vsso-14-1239-2:If (undefined) is VUID = 4500637 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>1239-2: fixed value = http://loinc.org if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.code.coding.version</t>
@@ -2456,10 +2460,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1239-3:undefined: if VUID = 4500637 then 3151-8 {null}</t>
-  </si>
-  <si>
-    <t>1239-3: fixed value = 3151-8 case VUID = 4500637</t>
+vsso-14-1239-3:If (undefined) is VUID = 4500637 then fixed value 3151-8 {null}</t>
+  </si>
+  <si>
+    <t>1239-3: fixed value = 3151-8 if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.code.coding.display</t>
@@ -2501,7 +2505,11 @@
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>1239: transform using Split_SpO2_value.Flow() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (120.5-1.4) case VUID = 4500637</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsso-14-1239:If VUID = 4500637 then transform (120.5-1.4) using Split_SpO2_value.Flow() {null}</t>
+  </si>
+  <si>
+    <t>1239: transform using Split_SpO2_value.Flow() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (120.5-1.4) if VUID = 4500637</t>
   </si>
   <si>
     <t>Vital.VitalSign.SupplementalO2</t>
@@ -2541,10 +2549,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1239-1:undefined: if VUID = 4500637 then L/min {null}</t>
-  </si>
-  <si>
-    <t>1239-1: fixed value = L/min case VUID = 4500637</t>
+vsso-14-1239-1:If (undefined) is VUID = 4500637 then fixed value L/min {null}</t>
+  </si>
+  <si>
+    <t>1239-1: fixed value = L/min if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.dataAbsentReason</t>
@@ -2604,10 +2612,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1240-2:undefined: if VUID = 4500637 then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>1240-2: fixed value = http://loinc.org case VUID = 4500637</t>
+vsso-14-1240-2:If (undefined) is VUID = 4500637 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>1240-2: fixed value = http://loinc.org if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.code.coding.version</t>
@@ -2617,10 +2625,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1240-3:undefined: if VUID = 4500637 then 3150-0 {null}</t>
-  </si>
-  <si>
-    <t>1240-3: fixed value = 3150-0 case VUID = 4500637</t>
+vsso-14-1240-3:If (undefined) is VUID = 4500637 then fixed value 3150-0 {null}</t>
+  </si>
+  <si>
+    <t>1240-3: fixed value = 3150-0 if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.code.coding.display</t>
@@ -2644,7 +2652,11 @@
     <t>Observation.component:Concentration.value[x].value</t>
   </si>
   <si>
-    <t>1240: transform using Split_SpO2_value.Consentration() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (120.5-1.4) case VUID = 4500637</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsso-14-1240:If VUID = 4500637 then transform (120.5-1.4) using Split_SpO2_value.Consentration() {null}</t>
+  </si>
+  <si>
+    <t>1240: transform using Split_SpO2_value.Consentration() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (120.5-1.4) if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.value[x].comparator</t>
@@ -2663,10 +2675,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1240-1:undefined: if VUID = 4500637 then % {null}</t>
-  </si>
-  <si>
-    <t>1240-1: fixed value = % case VUID = 4500637</t>
+vsso-14-1240-1:If (undefined) is VUID = 4500637 then fixed value % {null}</t>
+  </si>
+  <si>
+    <t>1240-1: fixed value = % if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.dataAbsentReason</t>
@@ -11411,16 +11423,16 @@
         <v>85</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>107</v>
+        <v>515</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>85</v>
@@ -11429,10 +11441,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -11443,10 +11455,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11472,20 +11484,20 @@
         <v>115</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>85</v>
@@ -11509,10 +11521,10 @@
         <v>175</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>85</v>
@@ -11530,7 +11542,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -11560,10 +11572,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -11574,10 +11586,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11603,14 +11615,14 @@
         <v>210</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -11659,7 +11671,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11689,10 +11701,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11703,10 +11715,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11732,14 +11744,14 @@
         <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
@@ -11788,7 +11800,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11797,7 +11809,7 @@
         <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>107</v>
@@ -11818,10 +11830,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11832,10 +11844,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11861,16 +11873,16 @@
         <v>115</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11919,7 +11931,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11934,7 +11946,7 @@
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>407</v>
@@ -11949,10 +11961,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11963,10 +11975,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11992,10 +12004,10 @@
         <v>210</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -12090,10 +12102,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -12215,13 +12227,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="B71" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="C71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>85</v>
@@ -12243,16 +12255,16 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12346,10 +12358,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12473,10 +12485,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12600,10 +12612,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12643,7 +12655,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>85</v>
@@ -12729,10 +12741,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12755,7 +12767,7 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>173</v>
@@ -12773,7 +12785,7 @@
         <v>85</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>85</v>
@@ -12856,10 +12868,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12885,10 +12897,10 @@
         <v>210</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12939,7 +12951,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12983,10 +12995,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13012,16 +13024,16 @@
         <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -13049,10 +13061,10 @@
         <v>228</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>85</v>
@@ -13070,7 +13082,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -13079,13 +13091,13 @@
         <v>95</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>85</v>
@@ -13103,7 +13115,7 @@
         <v>138</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -13114,14 +13126,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -13143,16 +13155,16 @@
         <v>172</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -13180,10 +13192,10 @@
         <v>228</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -13201,7 +13213,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -13228,27 +13240,27 @@
         <v>85</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13271,19 +13283,19 @@
         <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -13332,7 +13344,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -13362,10 +13374,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -13376,10 +13388,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13405,13 +13417,13 @@
         <v>172</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13441,7 +13453,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -13459,7 +13471,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13474,7 +13486,7 @@
         <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>85</v>
@@ -13486,27 +13498,27 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS80" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13532,16 +13544,16 @@
         <v>172</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -13570,7 +13582,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>85</v>
@@ -13588,7 +13600,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13603,7 +13615,7 @@
         <v>107</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>85</v>
@@ -13618,10 +13630,10 @@
         <v>85</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -13632,10 +13644,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13658,16 +13670,16 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13717,7 +13729,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13744,27 +13756,27 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13787,16 +13799,16 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13846,7 +13858,7 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13873,27 +13885,27 @@
         <v>85</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS83" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13916,19 +13928,19 @@
         <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>85</v>
@@ -13977,7 +13989,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13989,7 +14001,7 @@
         <v>85</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>85</v>
@@ -14007,10 +14019,10 @@
         <v>85</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -14021,10 +14033,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -14148,10 +14160,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14277,14 +14289,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -14306,10 +14318,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>197</v>
@@ -14364,7 +14376,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14408,10 +14420,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14434,13 +14446,13 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14491,7 +14503,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14500,7 +14512,7 @@
         <v>95</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>107</v>
@@ -14521,10 +14533,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -14535,10 +14547,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14561,13 +14573,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14618,7 +14630,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14627,7 +14639,7 @@
         <v>95</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>107</v>
@@ -14648,10 +14660,10 @@
         <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14662,10 +14674,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14691,16 +14703,16 @@
         <v>172</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14728,10 +14740,10 @@
         <v>119</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>85</v>
@@ -14749,7 +14761,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14776,13 +14788,13 @@
         <v>85</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14793,10 +14805,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14822,16 +14834,16 @@
         <v>172</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14856,13 +14868,13 @@
         <v>85</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>85</v>
@@ -14880,7 +14892,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14907,13 +14919,13 @@
         <v>85</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14924,10 +14936,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14950,17 +14962,17 @@
         <v>85</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -15009,7 +15021,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -15042,7 +15054,7 @@
         <v>85</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -15053,10 +15065,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15082,10 +15094,10 @@
         <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -15136,7 +15148,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -15166,10 +15178,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -15180,10 +15192,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15206,16 +15218,16 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -15265,7 +15277,7 @@
         <v>85</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -15295,10 +15307,10 @@
         <v>85</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
@@ -15309,10 +15321,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15335,16 +15347,16 @@
         <v>96</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15394,7 +15406,7 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15424,10 +15436,10 @@
         <v>85</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
@@ -15438,10 +15450,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15464,19 +15476,19 @@
         <v>96</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
@@ -15513,7 +15525,7 @@
         <v>85</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -15523,7 +15535,7 @@
         <v>144</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15535,7 +15547,7 @@
         <v>85</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>85</v>
@@ -15553,10 +15565,10 @@
         <v>85</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
@@ -15567,10 +15579,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15694,10 +15706,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15823,14 +15835,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15852,10 +15864,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>197</v>
@@ -15910,7 +15922,7 @@
         <v>85</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15954,10 +15966,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15983,16 +15995,16 @@
         <v>172</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
@@ -16041,7 +16053,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>95</v>
@@ -16068,7 +16080,7 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>396</v>
@@ -16085,10 +16097,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16114,13 +16126,13 @@
         <v>488</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>492</v>
@@ -16170,7 +16182,7 @@
         <v>144</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -16179,7 +16191,7 @@
         <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
@@ -16197,7 +16209,7 @@
         <v>85</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>497</v>
@@ -16214,10 +16226,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>501</v>
@@ -16245,13 +16257,13 @@
         <v>502</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>492</v>
@@ -16303,7 +16315,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -16312,13 +16324,13 @@
         <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>85</v>
@@ -16330,7 +16342,7 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>497</v>
@@ -16347,10 +16359,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16376,16 +16388,16 @@
         <v>172</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
@@ -16413,10 +16425,10 @@
         <v>228</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>85</v>
@@ -16434,7 +16446,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16443,13 +16455,13 @@
         <v>95</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>85</v>
@@ -16467,7 +16479,7 @@
         <v>138</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
@@ -16478,14 +16490,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -16507,16 +16519,16 @@
         <v>172</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
@@ -16544,10 +16556,10 @@
         <v>228</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>85</v>
@@ -16565,7 +16577,7 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16592,27 +16604,27 @@
         <v>85</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16638,16 +16650,16 @@
         <v>86</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>85</v>
@@ -16696,7 +16708,7 @@
         <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
@@ -16726,10 +16738,10 @@
         <v>85</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>85</v>
@@ -16740,13 +16752,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>85</v>
@@ -16768,19 +16780,19 @@
         <v>96</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>85</v>
@@ -16829,7 +16841,7 @@
         <v>85</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
@@ -16841,7 +16853,7 @@
         <v>85</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>85</v>
@@ -16859,10 +16871,10 @@
         <v>85</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>85</v>
@@ -16873,10 +16885,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -17000,10 +17012,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -17129,14 +17141,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -17158,10 +17170,10 @@
         <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>197</v>
@@ -17216,7 +17228,7 @@
         <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
@@ -17260,10 +17272,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17289,16 +17301,16 @@
         <v>172</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
@@ -17308,7 +17320,7 @@
         <v>85</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>85</v>
@@ -17347,7 +17359,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>95</v>
@@ -17374,7 +17386,7 @@
         <v>85</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>396</v>
@@ -17391,10 +17403,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17518,10 +17530,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17647,10 +17659,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17778,10 +17790,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17905,10 +17917,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -18034,10 +18046,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18133,10 +18145,10 @@
         <v>85</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>85</v>
@@ -18165,10 +18177,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18294,10 +18306,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18391,10 +18403,10 @@
         <v>85</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>85</v>
@@ -18423,10 +18435,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18552,10 +18564,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18683,10 +18695,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18814,10 +18826,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18843,13 +18855,13 @@
         <v>502</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>492</v>
@@ -18901,7 +18913,7 @@
         <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -18910,7 +18922,7 @@
         <v>95</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>107</v>
@@ -18928,7 +18940,7 @@
         <v>85</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>497</v>
@@ -18945,10 +18957,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -19072,10 +19084,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -19201,10 +19213,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19300,16 +19312,16 @@
         <v>85</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>107</v>
+        <v>795</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>85</v>
@@ -19318,10 +19330,10 @@
         <v>85</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>85</v>
@@ -19332,10 +19344,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19361,20 +19373,20 @@
         <v>115</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="R126" t="s" s="2">
         <v>85</v>
@@ -19398,10 +19410,10 @@
         <v>175</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>85</v>
@@ -19419,7 +19431,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19449,10 +19461,10 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19463,10 +19475,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19492,14 +19504,14 @@
         <v>210</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
@@ -19548,7 +19560,7 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -19578,10 +19590,10 @@
         <v>85</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
@@ -19592,10 +19604,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19621,21 +19633,21 @@
         <v>109</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>85</v>
@@ -19677,7 +19689,7 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -19686,7 +19698,7 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -19707,10 +19719,10 @@
         <v>85</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
@@ -19721,10 +19733,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19750,23 +19762,23 @@
         <v>115</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>85</v>
@@ -19808,7 +19820,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19820,10 +19832,10 @@
         <v>85</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>85</v>
@@ -19838,10 +19850,10 @@
         <v>85</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
@@ -19852,10 +19864,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19881,16 +19893,16 @@
         <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>85</v>
@@ -19918,10 +19930,10 @@
         <v>228</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>85</v>
@@ -19939,7 +19951,7 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
@@ -19948,7 +19960,7 @@
         <v>95</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>107</v>
@@ -19972,7 +19984,7 @@
         <v>138</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>
@@ -19983,14 +19995,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -20012,16 +20024,16 @@
         <v>172</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>85</v>
@@ -20049,10 +20061,10 @@
         <v>228</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>85</v>
@@ -20070,7 +20082,7 @@
         <v>85</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
@@ -20097,27 +20109,27 @@
         <v>85</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS131" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -20143,16 +20155,16 @@
         <v>86</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>85</v>
@@ -20201,7 +20213,7 @@
         <v>85</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>83</v>
@@ -20231,10 +20243,10 @@
         <v>85</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AR132" t="s" s="2">
         <v>85</v>
@@ -20245,13 +20257,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>85</v>
@@ -20273,19 +20285,19 @@
         <v>96</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>85</v>
@@ -20334,7 +20346,7 @@
         <v>85</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>83</v>
@@ -20346,7 +20358,7 @@
         <v>85</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>85</v>
@@ -20364,10 +20376,10 @@
         <v>85</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AR133" t="s" s="2">
         <v>85</v>
@@ -20378,10 +20390,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20505,10 +20517,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20634,14 +20646,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -20663,10 +20675,10 @@
         <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>197</v>
@@ -20721,7 +20733,7 @@
         <v>85</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>83</v>
@@ -20765,10 +20777,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20794,16 +20806,16 @@
         <v>172</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>85</v>
@@ -20813,7 +20825,7 @@
         <v>85</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>85</v>
@@ -20852,7 +20864,7 @@
         <v>85</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>95</v>
@@ -20879,7 +20891,7 @@
         <v>85</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>396</v>
@@ -20896,10 +20908,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -21023,10 +21035,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -21152,10 +21164,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21283,10 +21295,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21410,10 +21422,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21539,10 +21551,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21638,10 +21650,10 @@
         <v>85</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>85</v>
@@ -21670,10 +21682,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21799,10 +21811,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21896,10 +21908,10 @@
         <v>85</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>85</v>
@@ -21928,10 +21940,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -22057,10 +22069,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -22188,10 +22200,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22319,10 +22331,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22348,13 +22360,13 @@
         <v>502</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O149" t="s" s="2">
         <v>492</v>
@@ -22406,7 +22418,7 @@
         <v>85</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>83</v>
@@ -22415,7 +22427,7 @@
         <v>95</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>107</v>
@@ -22433,7 +22445,7 @@
         <v>85</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>497</v>
@@ -22450,10 +22462,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22577,10 +22589,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22706,10 +22718,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22805,16 +22817,16 @@
         <v>85</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>107</v>
+        <v>841</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>85</v>
@@ -22823,10 +22835,10 @@
         <v>85</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>85</v>
@@ -22837,10 +22849,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22866,20 +22878,20 @@
         <v>115</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q153" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="R153" t="s" s="2">
         <v>85</v>
@@ -22903,10 +22915,10 @@
         <v>175</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>85</v>
@@ -22924,7 +22936,7 @@
         <v>85</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>83</v>
@@ -22954,10 +22966,10 @@
         <v>85</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>85</v>
@@ -22968,10 +22980,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22997,14 +23009,14 @@
         <v>210</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>85</v>
@@ -23053,7 +23065,7 @@
         <v>85</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>83</v>
@@ -23083,10 +23095,10 @@
         <v>85</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>85</v>
@@ -23097,10 +23109,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23126,21 +23138,21 @@
         <v>109</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>85</v>
@@ -23182,7 +23194,7 @@
         <v>85</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>83</v>
@@ -23191,7 +23203,7 @@
         <v>95</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>107</v>
@@ -23212,10 +23224,10 @@
         <v>85</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>85</v>
@@ -23226,10 +23238,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -23255,23 +23267,23 @@
         <v>115</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="S156" t="s" s="2">
         <v>85</v>
@@ -23313,7 +23325,7 @@
         <v>85</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>83</v>
@@ -23325,10 +23337,10 @@
         <v>85</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>85</v>
@@ -23343,10 +23355,10 @@
         <v>85</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>85</v>
@@ -23357,10 +23369,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23386,16 +23398,16 @@
         <v>172</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>85</v>
@@ -23423,10 +23435,10 @@
         <v>228</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>85</v>
@@ -23444,7 +23456,7 @@
         <v>85</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>83</v>
@@ -23453,7 +23465,7 @@
         <v>95</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>107</v>
@@ -23477,7 +23489,7 @@
         <v>138</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>85</v>
@@ -23488,14 +23500,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -23517,16 +23529,16 @@
         <v>172</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>85</v>
@@ -23554,10 +23566,10 @@
         <v>228</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>85</v>
@@ -23575,7 +23587,7 @@
         <v>85</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>83</v>
@@ -23602,27 +23614,27 @@
         <v>85</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS158" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23648,16 +23660,16 @@
         <v>86</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>85</v>
@@ -23706,7 +23718,7 @@
         <v>85</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>83</v>
@@ -23736,10 +23748,10 @@
         <v>85</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>85</v>
@@ -23750,13 +23762,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>85</v>
@@ -23778,19 +23790,19 @@
         <v>96</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>85</v>
@@ -23839,7 +23851,7 @@
         <v>85</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>83</v>
@@ -23851,7 +23863,7 @@
         <v>85</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>85</v>
@@ -23869,10 +23881,10 @@
         <v>85</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>85</v>
@@ -23883,10 +23895,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -24010,10 +24022,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24139,14 +24151,14 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -24168,10 +24180,10 @@
         <v>140</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>197</v>
@@ -24226,7 +24238,7 @@
         <v>85</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>83</v>
@@ -24270,10 +24282,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24299,16 +24311,16 @@
         <v>172</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>85</v>
@@ -24318,7 +24330,7 @@
         <v>85</v>
       </c>
       <c r="S164" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="T164" t="s" s="2">
         <v>85</v>
@@ -24357,7 +24369,7 @@
         <v>85</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>95</v>
@@ -24372,7 +24384,7 @@
         <v>107</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>85</v>
@@ -24384,7 +24396,7 @@
         <v>85</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>396</v>
@@ -24401,10 +24413,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24430,13 +24442,13 @@
         <v>488</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O165" t="s" s="2">
         <v>492</v>
@@ -24486,7 +24498,7 @@
         <v>144</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>83</v>
@@ -24495,7 +24507,7 @@
         <v>95</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>107</v>
@@ -24513,7 +24525,7 @@
         <v>85</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>497</v>
@@ -24530,13 +24542,13 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>85</v>
@@ -24561,13 +24573,13 @@
         <v>172</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O166" t="s" s="2">
         <v>492</v>
@@ -24619,7 +24631,7 @@
         <v>85</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>83</v>
@@ -24628,7 +24640,7 @@
         <v>95</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>107</v>
@@ -24646,7 +24658,7 @@
         <v>85</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>497</v>
@@ -24663,10 +24675,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24790,10 +24802,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24919,10 +24931,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24986,7 +24998,7 @@
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>85</v>
@@ -25019,7 +25031,7 @@
         <v>107</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>85</v>
@@ -25048,10 +25060,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -25179,10 +25191,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25208,16 +25220,16 @@
         <v>172</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>85</v>
@@ -25245,10 +25257,10 @@
         <v>228</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>85</v>
@@ -25266,7 +25278,7 @@
         <v>85</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>83</v>
@@ -25275,7 +25287,7 @@
         <v>95</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>107</v>
@@ -25299,7 +25311,7 @@
         <v>138</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>85</v>
@@ -25310,14 +25322,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -25339,16 +25351,16 @@
         <v>172</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>85</v>
@@ -25376,10 +25388,10 @@
         <v>228</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>85</v>
@@ -25397,7 +25409,7 @@
         <v>85</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
@@ -25424,27 +25436,27 @@
         <v>85</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS172" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25470,16 +25482,16 @@
         <v>86</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>85</v>
@@ -25528,7 +25540,7 @@
         <v>85</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>83</v>
@@ -25558,10 +25570,10 @@
         <v>85</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>85</v>
@@ -25572,13 +25584,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>85</v>
@@ -25600,19 +25612,19 @@
         <v>96</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>85</v>
@@ -25661,7 +25673,7 @@
         <v>85</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>83</v>
@@ -25673,7 +25685,7 @@
         <v>85</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>85</v>
@@ -25691,10 +25703,10 @@
         <v>85</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>85</v>
@@ -25705,10 +25717,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25832,10 +25844,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25961,14 +25973,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -25990,10 +26002,10 @@
         <v>140</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>197</v>
@@ -26048,7 +26060,7 @@
         <v>85</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>83</v>
@@ -26092,10 +26104,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26121,16 +26133,16 @@
         <v>172</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>85</v>
@@ -26140,7 +26152,7 @@
         <v>85</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>85</v>
@@ -26179,7 +26191,7 @@
         <v>85</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>95</v>
@@ -26194,7 +26206,7 @@
         <v>107</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>85</v>
@@ -26206,7 +26218,7 @@
         <v>85</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>396</v>
@@ -26223,10 +26235,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -26252,13 +26264,13 @@
         <v>488</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O179" t="s" s="2">
         <v>492</v>
@@ -26308,7 +26320,7 @@
         <v>144</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>83</v>
@@ -26317,7 +26329,7 @@
         <v>95</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>107</v>
@@ -26335,7 +26347,7 @@
         <v>85</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP179" t="s" s="2">
         <v>497</v>
@@ -26352,13 +26364,13 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>85</v>
@@ -26383,13 +26395,13 @@
         <v>172</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O180" t="s" s="2">
         <v>492</v>
@@ -26441,7 +26453,7 @@
         <v>85</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>83</v>
@@ -26450,7 +26462,7 @@
         <v>95</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>107</v>
@@ -26468,7 +26480,7 @@
         <v>85</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>497</v>
@@ -26485,10 +26497,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26612,10 +26624,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26741,10 +26753,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26808,7 +26820,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>85</v>
@@ -26841,7 +26853,7 @@
         <v>107</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>85</v>
@@ -26870,10 +26882,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -27001,10 +27013,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27030,16 +27042,16 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>85</v>
@@ -27067,10 +27079,10 @@
         <v>228</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>85</v>
@@ -27088,7 +27100,7 @@
         <v>85</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>83</v>
@@ -27097,7 +27109,7 @@
         <v>95</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>107</v>
@@ -27121,7 +27133,7 @@
         <v>138</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>85</v>
@@ -27132,14 +27144,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -27161,16 +27173,16 @@
         <v>172</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>85</v>
@@ -27198,10 +27210,10 @@
         <v>228</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>85</v>
@@ -27219,7 +27231,7 @@
         <v>85</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>83</v>
@@ -27246,27 +27258,27 @@
         <v>85</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP186" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AQ186" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AR186" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS186" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27292,16 +27304,16 @@
         <v>86</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>85</v>
@@ -27350,7 +27362,7 @@
         <v>85</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>83</v>
@@ -27380,10 +27392,10 @@
         <v>85</v>
       </c>
       <c r="AP187" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ187" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AR187" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$148</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6534" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6162" uniqueCount="828">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,6 +968,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t>value:coding.code}
+value:coding.system}</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat</t>
+  </si>
+  <si>
+    <t>VSCat</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -978,29 +1000,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t>value:coding.code}
-value:coding.system}</t>
-  </si>
-  <si>
     <t>658: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#vital-signs</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:VSCat</t>
-  </si>
-  <si>
-    <t>VSCat</t>
   </si>
   <si>
     <t>Observation.category:VSCat.id</t>
@@ -1791,9 +1791,6 @@
   <si>
     <t>obs-6
 vs-2</t>
-  </si>
-  <si>
-    <t>1793: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2270,12 +2267,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>2193: target not supported</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -2291,9 +2282,6 @@
   <si>
     <t>obs-6
 vs-3</t>
-  </si>
-  <si>
-    <t>1794: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2341,10 +2329,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1239-2:If VUID = 4500637 then fixed value http://loinc.org#3151-8 {true}</t>
-  </si>
-  <si>
-    <t>1239-2: fixed value = http://loinc.org#3151-8 if VUID = 4500637</t>
+vsso-14-1239-3:If VUID = 4500637 then fixed value http://loinc.org#3151-8 {true}</t>
+  </si>
+  <si>
+    <t>1239-3: fixed value = http://loinc.org#3151-8 if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.value[x]</t>
@@ -2391,6 +2379,13 @@
   </si>
   <si>
     <t>Observation.component.value[x].unit</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsso-14-1239-2:If VUID = 4500637 then fixed value L/min {true}</t>
+  </si>
+  <si>
+    <t>1239-2: fixed value = L/min if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.value[x].system</t>
@@ -2460,10 +2455,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsso-14-1240-2:If VUID = 4500637 then fixed value http://loinc.org#3150-0 {true}</t>
-  </si>
-  <si>
-    <t>1240-2: fixed value = http://loinc.org#3150-0 if VUID = 4500637</t>
+vsso-14-1240-3:If VUID = 4500637 then fixed value http://loinc.org#3150-0 {true}</t>
+  </si>
+  <si>
+    <t>1240-3: fixed value = http://loinc.org#3150-0 if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.value[x]</t>
@@ -2489,6 +2484,13 @@
   </si>
   <si>
     <t>Observation.component:Concentration.value[x].unit</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsso-14-1240-2:If VUID = 4500637 then fixed value % {true}</t>
+  </si>
+  <si>
+    <t>1240-2: fixed value = % if VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.value[x].system</t>
@@ -2555,18 +2557,6 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
     <t>see mapping [VF_VitalsPrecondition](ConceptMap-VF-VitalsPrecondition.html)</t>
   </si>
   <si>
@@ -2576,12 +2566,6 @@
     <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
-    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component:va-pre-condition.dataAbsentReason</t>
   </si>
   <si>
@@ -2618,15 +2602,6 @@
     <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
     <t>see mapping [VF_VitalsQualifyingDevice](ConceptMap-VF-VitalsQualifyingDevice.html)</t>
   </si>
   <si>
@@ -2634,9 +2609,6 @@
   </si>
   <si>
     <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.text</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.dataAbsentReason</t>
@@ -2962,10 +2934,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS157"/>
+  <dimension ref="A1:AS148"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="85.0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="75.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.28515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -7183,7 +7155,7 @@
         <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>307</v>
+        <v>85</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>85</v>
@@ -7201,16 +7173,16 @@
         <v>119</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB33" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7235,28 +7207,28 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AS33" t="s" s="2">
         <v>85</v>
@@ -7264,13 +7236,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>302</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -7314,7 +7286,7 @@
         <v>85</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>85</v>
+        <v>314</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>85</v>
@@ -7332,10 +7304,10 @@
         <v>119</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -7368,7 +7340,7 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>85</v>
+        <v>315</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -7386,10 +7358,10 @@
         <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AS34" t="s" s="2">
         <v>85</v>
@@ -11915,7 +11887,7 @@
         <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>569</v>
+        <v>85</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>85</v>
@@ -11933,7 +11905,7 @@
         <v>138</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11944,14 +11916,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11973,16 +11945,16 @@
         <v>172</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -12010,11 +11982,11 @@
         <v>230</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>578</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
       </c>
@@ -12031,7 +12003,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -12058,27 +12030,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AQ70" t="s" s="2">
+      <c r="AR70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS70" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS70" t="s" s="2">
-        <v>582</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12101,19 +12073,19 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -12162,7 +12134,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -12192,10 +12164,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -12206,10 +12178,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12235,13 +12207,13 @@
         <v>172</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12270,11 +12242,11 @@
         <v>175</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
       </c>
@@ -12291,7 +12263,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12306,7 +12278,7 @@
         <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>85</v>
@@ -12318,27 +12290,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AP72" t="s" s="2">
+      <c r="AQ72" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AQ72" t="s" s="2">
+      <c r="AR72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS72" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>601</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12364,16 +12336,16 @@
         <v>172</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -12401,11 +12373,11 @@
         <v>175</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
       </c>
@@ -12422,7 +12394,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -12437,7 +12409,7 @@
         <v>107</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>85</v>
@@ -12452,10 +12424,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -12466,10 +12438,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12492,16 +12464,16 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12551,7 +12523,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12578,27 +12550,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="AP74" t="s" s="2">
+      <c r="AQ74" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AQ74" t="s" s="2">
+      <c r="AR74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS74" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AR74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS74" t="s" s="2">
-        <v>620</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12621,16 +12593,16 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12680,7 +12652,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12707,27 +12679,27 @@
         <v>85</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AQ75" t="s" s="2">
+      <c r="AR75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS75" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS75" t="s" s="2">
-        <v>629</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12750,19 +12722,19 @@
         <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12811,7 +12783,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12823,28 +12795,28 @@
         <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AK76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
@@ -12855,10 +12827,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12982,10 +12954,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13111,14 +13083,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -13140,10 +13112,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>199</v>
@@ -13198,7 +13170,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -13242,10 +13214,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13268,13 +13240,13 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -13325,7 +13297,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13334,7 +13306,7 @@
         <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>107</v>
@@ -13355,10 +13327,10 @@
         <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
@@ -13369,10 +13341,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13395,13 +13367,13 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -13452,7 +13424,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13461,7 +13433,7 @@
         <v>95</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>107</v>
@@ -13482,10 +13454,10 @@
         <v>85</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -13496,10 +13468,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13525,16 +13497,16 @@
         <v>172</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13562,11 +13534,11 @@
         <v>119</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>663</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
       </c>
@@ -13583,7 +13555,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13610,13 +13582,13 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AP82" t="s" s="2">
-        <v>665</v>
-      </c>
       <c r="AQ82" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13627,10 +13599,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13656,16 +13628,16 @@
         <v>172</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>85</v>
@@ -13690,14 +13662,14 @@
         <v>85</v>
       </c>
       <c r="X83" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="Y83" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="Y83" t="s" s="2">
+      <c r="Z83" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="Z83" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="AA83" t="s" s="2">
         <v>85</v>
       </c>
@@ -13714,7 +13686,7 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13741,13 +13713,13 @@
         <v>85</v>
       </c>
       <c r="AO83" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AP83" t="s" s="2">
-        <v>665</v>
-      </c>
       <c r="AQ83" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
@@ -13758,10 +13730,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13784,17 +13756,17 @@
         <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>85</v>
@@ -13843,7 +13815,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13876,7 +13848,7 @@
         <v>85</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13887,10 +13859,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13916,10 +13888,10 @@
         <v>212</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13970,7 +13942,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -14000,10 +13972,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -14014,10 +13986,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14040,16 +14012,16 @@
         <v>96</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -14099,7 +14071,7 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -14129,10 +14101,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -14143,10 +14115,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14169,16 +14141,16 @@
         <v>96</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -14228,7 +14200,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14258,10 +14230,10 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -14272,10 +14244,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14298,19 +14270,19 @@
         <v>96</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -14347,7 +14319,7 @@
         <v>85</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AC88" s="2"/>
       <c r="AD88" t="s" s="2">
@@ -14357,7 +14329,7 @@
         <v>144</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14369,28 +14341,28 @@
         <v>85</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP88" t="s" s="2">
+      <c r="AQ88" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -14401,10 +14373,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14528,10 +14500,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14657,14 +14629,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -14686,10 +14658,10 @@
         <v>140</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>199</v>
@@ -14744,7 +14716,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14788,10 +14760,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14817,16 +14789,16 @@
         <v>172</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14875,7 +14847,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>95</v>
@@ -14902,7 +14874,7 @@
         <v>85</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>398</v>
@@ -14919,10 +14891,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14948,13 +14920,13 @@
         <v>491</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>495</v>
@@ -14994,17 +14966,19 @@
         <v>85</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AC93" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD93" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -15013,7 +14987,7 @@
         <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>107</v>
@@ -15031,7 +15005,7 @@
         <v>85</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>500</v>
@@ -15048,14 +15022,12 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>85</v>
       </c>
@@ -15073,22 +15045,22 @@
         <v>85</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>505</v>
+        <v>172</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>495</v>
+        <v>565</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -15116,10 +15088,10 @@
         <v>230</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>496</v>
+        <v>566</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>497</v>
+        <v>567</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>85</v>
@@ -15137,7 +15109,7 @@
         <v>85</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -15146,13 +15118,13 @@
         <v>95</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>721</v>
+        <v>85</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>85</v>
@@ -15164,41 +15136,41 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>719</v>
+        <v>85</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>500</v>
+        <v>138</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>501</v>
+        <v>569</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>502</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>85</v>
@@ -15210,16 +15182,16 @@
         <v>172</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>723</v>
+        <v>572</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>724</v>
+        <v>573</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>725</v>
+        <v>574</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -15247,10 +15219,10 @@
         <v>230</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>85</v>
@@ -15268,22 +15240,22 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>726</v>
+        <v>85</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>727</v>
+        <v>85</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>85</v>
@@ -15295,31 +15267,31 @@
         <v>85</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>85</v>
+        <v>578</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>138</v>
+        <v>579</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS95" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>572</v>
+        <v>85</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -15338,19 +15310,19 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>573</v>
+        <v>726</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>574</v>
+        <v>727</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
@@ -15375,13 +15347,13 @@
         <v>85</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>578</v>
+        <v>85</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>85</v>
@@ -15399,7 +15371,7 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15426,29 +15398,31 @@
         <v>85</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>579</v>
+        <v>85</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>580</v>
+        <v>636</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>581</v>
+        <v>637</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS96" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>85</v>
       </c>
@@ -15457,19 +15431,19 @@
         <v>83</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>86</v>
+        <v>630</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>730</v>
@@ -15478,10 +15452,10 @@
         <v>731</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>634</v>
+        <v>698</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>635</v>
+        <v>699</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -15530,7 +15504,7 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15542,7 +15516,7 @@
         <v>85</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>107</v>
+        <v>701</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>85</v>
@@ -15560,10 +15534,10 @@
         <v>85</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>637</v>
+        <v>702</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>638</v>
+        <v>703</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>85</v>
@@ -15577,11 +15551,9 @@
         <v>732</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>733</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>85</v>
       </c>
@@ -15593,29 +15565,25 @@
         <v>95</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>631</v>
+        <v>212</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>734</v>
+        <v>154</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>85</v>
       </c>
@@ -15663,19 +15631,19 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>697</v>
+        <v>156</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>702</v>
+        <v>85</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>85</v>
@@ -15693,10 +15661,10 @@
         <v>85</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>703</v>
+        <v>85</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>704</v>
+        <v>158</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>
@@ -15707,21 +15675,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>705</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>85</v>
@@ -15733,15 +15701,17 @@
         <v>85</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>85</v>
@@ -15790,19 +15760,19 @@
         <v>85</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>85</v>
@@ -15834,14 +15804,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>706</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>196</v>
+        <v>641</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -15854,24 +15824,26 @@
         <v>85</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>214</v>
+        <v>642</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>215</v>
+        <v>643</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
       </c>
@@ -15919,7 +15891,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>162</v>
+        <v>644</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15952,7 +15924,7 @@
         <v>85</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>85</v>
@@ -15963,45 +15935,45 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>707</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>642</v>
+        <v>85</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>199</v>
+        <v>710</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>200</v>
+        <v>711</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>85</v>
@@ -16011,7 +15983,7 @@
         <v>85</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>85</v>
+        <v>736</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>85</v>
@@ -16026,13 +15998,13 @@
         <v>85</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>85</v>
@@ -16050,22 +16022,22 @@
         <v>85</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>645</v>
+        <v>707</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>146</v>
+        <v>737</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>85</v>
+        <v>738</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>85</v>
@@ -16077,16 +16049,16 @@
         <v>85</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>85</v>
+        <v>712</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>138</v>
+        <v>399</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>85</v>
@@ -16097,7 +16069,7 @@
         <v>739</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16105,7 +16077,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>95</v>
@@ -16120,19 +16092,19 @@
         <v>96</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>172</v>
+        <v>505</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>712</v>
+        <v>495</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -16142,7 +16114,7 @@
         <v>85</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>740</v>
+        <v>85</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>85</v>
@@ -16160,10 +16132,10 @@
         <v>230</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>395</v>
+        <v>497</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -16181,22 +16153,22 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>741</v>
+        <v>107</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>742</v>
+        <v>85</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>85</v>
@@ -16208,27 +16180,27 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>398</v>
+        <v>500</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>399</v>
+        <v>501</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16242,29 +16214,25 @@
         <v>95</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>505</v>
+        <v>212</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>715</v>
+        <v>154</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>85</v>
       </c>
@@ -16288,13 +16256,13 @@
         <v>85</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>497</v>
+        <v>85</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>85</v>
@@ -16312,7 +16280,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>714</v>
+        <v>156</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16321,10 +16289,10 @@
         <v>95</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>718</v>
+        <v>85</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>85</v>
@@ -16339,38 +16307,38 @@
         <v>85</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>719</v>
+        <v>85</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>501</v>
+        <v>158</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS103" t="s" s="2">
-        <v>502</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>85</v>
@@ -16382,15 +16350,17 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>85</v>
@@ -16427,31 +16397,31 @@
         <v>85</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>85</v>
@@ -16483,44 +16453,46 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>140</v>
+        <v>512</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>214</v>
+        <v>513</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>215</v>
+        <v>514</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>85</v>
       </c>
@@ -16556,40 +16528,40 @@
         <v>85</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>162</v>
+        <v>517</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>146</v>
+        <v>746</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>85</v>
+        <v>747</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>85</v>
+        <v>748</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>85</v>
+        <v>749</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>85</v>
@@ -16598,10 +16570,10 @@
         <v>85</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>85</v>
+        <v>522</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>158</v>
+        <v>523</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>85</v>
@@ -16612,10 +16584,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16623,39 +16595,39 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I106" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>512</v>
+        <v>115</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="R106" t="s" s="2">
         <v>85</v>
       </c>
@@ -16675,13 +16647,13 @@
         <v>85</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>85</v>
+        <v>531</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>85</v>
@@ -16699,7 +16671,7 @@
         <v>85</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
@@ -16711,16 +16683,16 @@
         <v>85</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>750</v>
+        <v>107</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>751</v>
+        <v>85</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>752</v>
+        <v>85</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>753</v>
+        <v>85</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>85</v>
@@ -16729,10 +16701,10 @@
         <v>85</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>85</v>
@@ -16743,10 +16715,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16754,39 +16726,37 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q107" t="s" s="2">
-        <v>529</v>
-      </c>
+      <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
         <v>85</v>
       </c>
@@ -16806,13 +16776,13 @@
         <v>85</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>531</v>
+        <v>85</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -16830,7 +16800,7 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -16842,10 +16812,10 @@
         <v>85</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>107</v>
+        <v>754</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>85</v>
+        <v>755</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>85</v>
@@ -16860,10 +16830,10 @@
         <v>85</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>85</v>
@@ -16900,24 +16870,24 @@
         <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>85</v>
+        <v>758</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>85</v>
@@ -16959,7 +16929,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -16968,7 +16938,7 @@
         <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>107</v>
@@ -16992,7 +16962,7 @@
         <v>541</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AR108" t="s" s="2">
         <v>85</v>
@@ -17003,10 +16973,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17029,24 +16999,26 @@
         <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="O109" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>85</v>
@@ -17088,7 +17060,7 @@
         <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
@@ -17097,13 +17069,13 @@
         <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>549</v>
+        <v>85</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>107</v>
+        <v>763</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>85</v>
+        <v>764</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>85</v>
@@ -17121,7 +17093,7 @@
         <v>541</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>85</v>
@@ -17132,10 +17104,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>762</v>
+        <v>719</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17143,7 +17115,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>95</v>
@@ -17155,29 +17127,29 @@
         <v>85</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>553</v>
+        <v>720</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>554</v>
+        <v>721</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>764</v>
+        <v>85</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>85</v>
@@ -17195,13 +17167,13 @@
         <v>85</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>85</v>
@@ -17219,7 +17191,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>557</v>
+        <v>719</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17228,13 +17200,13 @@
         <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>765</v>
+        <v>107</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>766</v>
+        <v>85</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>85</v>
@@ -17249,10 +17221,10 @@
         <v>85</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>541</v>
+        <v>138</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
@@ -17263,24 +17235,24 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>85</v>
@@ -17292,16 +17264,16 @@
         <v>172</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>723</v>
+        <v>572</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>724</v>
+        <v>573</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>725</v>
+        <v>574</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>85</v>
@@ -17329,10 +17301,10 @@
         <v>230</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>85</v>
@@ -17350,16 +17322,16 @@
         <v>85</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>726</v>
+        <v>85</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>107</v>
@@ -17377,31 +17349,31 @@
         <v>85</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>85</v>
+        <v>578</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>138</v>
+        <v>579</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS111" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>572</v>
+        <v>85</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -17420,19 +17392,19 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>573</v>
+        <v>726</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>574</v>
+        <v>727</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>85</v>
@@ -17457,13 +17429,13 @@
         <v>85</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>578</v>
+        <v>85</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>85</v>
@@ -17481,7 +17453,7 @@
         <v>85</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -17508,29 +17480,31 @@
         <v>85</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>579</v>
+        <v>85</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>580</v>
+        <v>636</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>581</v>
+        <v>637</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS112" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="B113" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>85</v>
       </c>
@@ -17539,31 +17513,31 @@
         <v>83</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>86</v>
+        <v>630</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>731</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>634</v>
+        <v>698</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>635</v>
+        <v>699</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>85</v>
@@ -17612,7 +17586,7 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -17624,7 +17598,7 @@
         <v>85</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>107</v>
+        <v>701</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>85</v>
@@ -17642,10 +17616,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>637</v>
+        <v>702</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>638</v>
+        <v>703</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17656,14 +17630,12 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>771</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>85</v>
       </c>
@@ -17675,29 +17647,25 @@
         <v>95</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>631</v>
+        <v>212</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>772</v>
+        <v>154</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>85</v>
       </c>
@@ -17745,19 +17713,19 @@
         <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>697</v>
+        <v>156</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>702</v>
+        <v>85</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>85</v>
@@ -17775,10 +17743,10 @@
         <v>85</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>703</v>
+        <v>85</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>704</v>
+        <v>158</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>85</v>
@@ -17789,21 +17757,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>705</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>85</v>
@@ -17815,15 +17783,17 @@
         <v>85</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>85</v>
@@ -17872,19 +17842,19 @@
         <v>85</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>85</v>
@@ -17916,14 +17886,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>706</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>196</v>
+        <v>641</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -17936,24 +17906,26 @@
         <v>85</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>214</v>
+        <v>642</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>215</v>
+        <v>643</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="O116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>85</v>
       </c>
@@ -18001,7 +17973,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>162</v>
+        <v>644</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -18034,7 +18006,7 @@
         <v>85</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
@@ -18045,45 +18017,45 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>707</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>642</v>
+        <v>85</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>199</v>
+        <v>710</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>200</v>
+        <v>711</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -18093,7 +18065,7 @@
         <v>85</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>85</v>
+        <v>775</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>85</v>
@@ -18108,13 +18080,13 @@
         <v>85</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>85</v>
@@ -18132,22 +18104,22 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>645</v>
+        <v>707</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>146</v>
+        <v>776</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>85</v>
+        <v>777</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>85</v>
@@ -18159,16 +18131,16 @@
         <v>85</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>85</v>
+        <v>712</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>138</v>
+        <v>399</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AS117" t="s" s="2">
         <v>85</v>
@@ -18176,10 +18148,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18187,7 +18159,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>95</v>
@@ -18202,19 +18174,19 @@
         <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>172</v>
+        <v>505</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>712</v>
+        <v>495</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
@@ -18224,7 +18196,7 @@
         <v>85</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>777</v>
+        <v>85</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>85</v>
@@ -18242,10 +18214,10 @@
         <v>230</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>395</v>
+        <v>497</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>85</v>
@@ -18263,22 +18235,22 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>778</v>
+        <v>107</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>779</v>
+        <v>85</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>85</v>
@@ -18290,27 +18262,27 @@
         <v>85</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>398</v>
+        <v>500</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>399</v>
+        <v>501</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AS118" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18324,29 +18296,25 @@
         <v>95</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>505</v>
+        <v>212</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>715</v>
+        <v>154</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>85</v>
       </c>
@@ -18370,13 +18338,13 @@
         <v>85</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>497</v>
+        <v>85</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>85</v>
@@ -18394,7 +18362,7 @@
         <v>85</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>714</v>
+        <v>156</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -18403,10 +18371,10 @@
         <v>95</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>718</v>
+        <v>85</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>85</v>
@@ -18421,38 +18389,38 @@
         <v>85</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>719</v>
+        <v>85</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>501</v>
+        <v>158</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS119" t="s" s="2">
-        <v>502</v>
+        <v>85</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>85</v>
@@ -18464,15 +18432,17 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>85</v>
@@ -18509,31 +18479,31 @@
         <v>85</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>85</v>
@@ -18565,44 +18535,46 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>140</v>
+        <v>512</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>214</v>
+        <v>513</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>215</v>
+        <v>514</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>85</v>
       </c>
@@ -18638,40 +18610,40 @@
         <v>85</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>162</v>
+        <v>517</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>146</v>
+        <v>782</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>85</v>
+        <v>783</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>85</v>
+        <v>748</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>85</v>
+        <v>749</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>85</v>
@@ -18680,10 +18652,10 @@
         <v>85</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>85</v>
+        <v>522</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>158</v>
+        <v>523</v>
       </c>
       <c r="AR121" t="s" s="2">
         <v>85</v>
@@ -18694,10 +18666,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18705,39 +18677,39 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H122" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I122" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>512</v>
+        <v>115</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q122" s="2"/>
+      <c r="Q122" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="R122" t="s" s="2">
         <v>85</v>
       </c>
@@ -18757,13 +18729,13 @@
         <v>85</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>85</v>
+        <v>531</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>85</v>
@@ -18781,7 +18753,7 @@
         <v>85</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -18793,16 +18765,16 @@
         <v>85</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>784</v>
+        <v>107</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>785</v>
+        <v>85</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>752</v>
+        <v>85</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>753</v>
+        <v>85</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>85</v>
@@ -18811,10 +18783,10 @@
         <v>85</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="AR122" t="s" s="2">
         <v>85</v>
@@ -18825,10 +18797,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18836,39 +18808,37 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q123" t="s" s="2">
-        <v>529</v>
-      </c>
+      <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
         <v>85</v>
       </c>
@@ -18888,13 +18858,13 @@
         <v>85</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>531</v>
+        <v>85</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>85</v>
@@ -18912,7 +18882,7 @@
         <v>85</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -18924,10 +18894,10 @@
         <v>85</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>107</v>
+        <v>786</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>85</v>
+        <v>787</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>85</v>
@@ -18942,10 +18912,10 @@
         <v>85</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>85</v>
@@ -18956,7 +18926,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>757</v>
@@ -18982,24 +18952,24 @@
         <v>96</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q124" s="2"/>
       <c r="R124" t="s" s="2">
-        <v>85</v>
+        <v>758</v>
       </c>
       <c r="S124" t="s" s="2">
         <v>85</v>
@@ -19041,7 +19011,7 @@
         <v>85</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
@@ -19050,7 +19020,7 @@
         <v>95</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>107</v>
@@ -19074,7 +19044,7 @@
         <v>541</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>85</v>
@@ -19085,10 +19055,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19111,24 +19081,26 @@
         <v>96</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="O125" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>85</v>
@@ -19170,7 +19142,7 @@
         <v>85</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>83</v>
@@ -19179,13 +19151,13 @@
         <v>95</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>549</v>
+        <v>85</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>107</v>
+        <v>791</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>85</v>
+        <v>792</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>85</v>
@@ -19203,7 +19175,7 @@
         <v>541</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>85</v>
@@ -19214,10 +19186,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>762</v>
+        <v>719</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19225,7 +19197,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>95</v>
@@ -19237,29 +19209,29 @@
         <v>85</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>553</v>
+        <v>720</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>554</v>
+        <v>721</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>790</v>
+        <v>85</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>85</v>
@@ -19277,13 +19249,13 @@
         <v>85</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>85</v>
@@ -19301,7 +19273,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>557</v>
+        <v>719</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19310,13 +19282,13 @@
         <v>95</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>791</v>
+        <v>107</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>792</v>
+        <v>85</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>85</v>
@@ -19331,10 +19303,10 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>541</v>
+        <v>138</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19345,24 +19317,24 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>85</v>
@@ -19374,16 +19346,16 @@
         <v>172</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>723</v>
+        <v>572</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>724</v>
+        <v>573</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>725</v>
+        <v>574</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
@@ -19411,10 +19383,10 @@
         <v>230</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>85</v>
@@ -19432,16 +19404,16 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>726</v>
+        <v>85</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>107</v>
@@ -19459,31 +19431,31 @@
         <v>85</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>85</v>
+        <v>578</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>138</v>
+        <v>579</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS127" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>572</v>
+        <v>85</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -19502,19 +19474,19 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>573</v>
+        <v>726</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>574</v>
+        <v>727</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>85</v>
@@ -19539,13 +19511,13 @@
         <v>85</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>578</v>
+        <v>85</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>85</v>
@@ -19563,7 +19535,7 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -19590,29 +19562,31 @@
         <v>85</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>579</v>
+        <v>85</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>580</v>
+        <v>636</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>581</v>
+        <v>637</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS128" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>696</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>797</v>
+      </c>
       <c r="D129" t="s" s="2">
         <v>85</v>
       </c>
@@ -19621,31 +19595,31 @@
         <v>83</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>86</v>
+        <v>630</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>730</v>
+        <v>697</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>731</v>
+        <v>697</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>634</v>
+        <v>698</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>635</v>
+        <v>699</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
@@ -19694,7 +19668,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19706,7 +19680,7 @@
         <v>85</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>107</v>
+        <v>701</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>85</v>
@@ -19724,10 +19698,10 @@
         <v>85</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>637</v>
+        <v>702</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>638</v>
+        <v>703</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
@@ -19738,14 +19712,12 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>797</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>85</v>
       </c>
@@ -19757,29 +19729,25 @@
         <v>95</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>631</v>
+        <v>212</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>698</v>
+        <v>154</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>700</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>85</v>
       </c>
@@ -19827,19 +19795,19 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>697</v>
+        <v>156</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>702</v>
+        <v>85</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>85</v>
@@ -19857,10 +19825,10 @@
         <v>85</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>703</v>
+        <v>85</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>704</v>
+        <v>158</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>
@@ -19871,21 +19839,21 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>705</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>85</v>
@@ -19897,15 +19865,17 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>85</v>
@@ -19954,19 +19924,19 @@
         <v>85</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>85</v>
@@ -19998,14 +19968,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>706</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>196</v>
+        <v>641</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -20018,24 +19988,26 @@
         <v>85</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>214</v>
+        <v>642</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>215</v>
+        <v>643</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="O132" s="2"/>
+      <c r="O132" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>85</v>
       </c>
@@ -20083,7 +20055,7 @@
         <v>85</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>162</v>
+        <v>644</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>83</v>
@@ -20116,7 +20088,7 @@
         <v>85</v>
       </c>
       <c r="AQ132" t="s" s="2">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AR132" t="s" s="2">
         <v>85</v>
@@ -20127,45 +20099,45 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>707</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>642</v>
+        <v>85</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J133" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>199</v>
+        <v>710</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>200</v>
+        <v>711</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>85</v>
@@ -20175,7 +20147,7 @@
         <v>85</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>85</v>
+        <v>802</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>85</v>
@@ -20190,13 +20162,13 @@
         <v>85</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>85</v>
@@ -20214,22 +20186,22 @@
         <v>85</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>645</v>
+        <v>707</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>85</v>
+        <v>803</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>85</v>
@@ -20241,16 +20213,16 @@
         <v>85</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>85</v>
+        <v>712</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>138</v>
+        <v>399</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AS133" t="s" s="2">
         <v>85</v>
@@ -20258,10 +20230,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20269,7 +20241,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>95</v>
@@ -20284,19 +20256,19 @@
         <v>96</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>172</v>
+        <v>491</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>712</v>
+        <v>495</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>85</v>
@@ -20306,7 +20278,7 @@
         <v>85</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>802</v>
+        <v>85</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>85</v>
@@ -20324,43 +20296,41 @@
         <v>230</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>395</v>
+        <v>497</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>803</v>
+        <v>85</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>85</v>
@@ -20372,29 +20342,31 @@
         <v>85</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>398</v>
+        <v>500</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>399</v>
+        <v>501</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AS134" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C135" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>806</v>
+      </c>
       <c r="D135" t="s" s="2">
         <v>85</v>
       </c>
@@ -20415,16 +20387,16 @@
         <v>96</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>491</v>
+        <v>172</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="O135" t="s" s="2">
         <v>495</v>
@@ -20452,29 +20424,31 @@
         <v>85</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>496</v>
+        <v>807</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>497</v>
+        <v>808</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AC135" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD135" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>83</v>
@@ -20483,25 +20457,25 @@
         <v>95</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>85</v>
+        <v>809</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>500</v>
@@ -20518,14 +20492,12 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>806</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>85</v>
       </c>
@@ -20543,22 +20515,22 @@
         <v>85</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K136" t="s" s="2">
         <v>172</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>495</v>
+        <v>565</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>85</v>
@@ -20586,10 +20558,10 @@
         <v>230</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>496</v>
+        <v>566</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>497</v>
+        <v>567</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>85</v>
@@ -20607,7 +20579,7 @@
         <v>85</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>83</v>
@@ -20616,7 +20588,7 @@
         <v>95</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>107</v>
@@ -20634,38 +20606,38 @@
         <v>85</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>719</v>
+        <v>85</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>500</v>
+        <v>138</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>501</v>
+        <v>569</v>
       </c>
       <c r="AR136" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS136" t="s" s="2">
-        <v>502</v>
+        <v>85</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>85</v>
@@ -20677,16 +20649,20 @@
         <v>85</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>154</v>
+        <v>572</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>85</v>
       </c>
@@ -20710,13 +20686,13 @@
         <v>85</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>85</v>
+        <v>577</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>85</v>
@@ -20734,19 +20710,19 @@
         <v>85</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>156</v>
+        <v>724</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>85</v>
@@ -20761,31 +20737,31 @@
         <v>85</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>85</v>
+        <v>578</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>85</v>
+        <v>579</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>158</v>
+        <v>580</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS137" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>747</v>
+        <v>725</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20804,18 +20780,20 @@
         <v>85</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>214</v>
+        <v>726</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>215</v>
+        <v>727</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O138" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>634</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>85</v>
       </c>
@@ -20851,19 +20829,19 @@
         <v>85</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>162</v>
+        <v>725</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>83</v>
@@ -20875,7 +20853,7 @@
         <v>85</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>85</v>
@@ -20893,10 +20871,10 @@
         <v>85</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>85</v>
+        <v>636</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>158</v>
+        <v>637</v>
       </c>
       <c r="AR138" t="s" s="2">
         <v>85</v>
@@ -20907,12 +20885,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>696</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>814</v>
+      </c>
       <c r="D139" t="s" s="2">
         <v>85</v>
       </c>
@@ -20921,7 +20901,7 @@
         <v>83</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>96</v>
@@ -20933,19 +20913,19 @@
         <v>96</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>322</v>
+        <v>630</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>323</v>
+        <v>697</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>324</v>
+        <v>697</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>325</v>
+        <v>698</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>326</v>
+        <v>699</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>85</v>
@@ -20970,13 +20950,13 @@
         <v>85</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>811</v>
+        <v>85</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>812</v>
+        <v>85</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>85</v>
@@ -20994,7 +20974,7 @@
         <v>85</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>327</v>
+        <v>696</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>83</v>
@@ -21006,16 +20986,16 @@
         <v>85</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>107</v>
+        <v>701</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>813</v>
+        <v>85</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>85</v>
@@ -21024,10 +21004,10 @@
         <v>85</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>328</v>
+        <v>702</v>
       </c>
       <c r="AQ139" t="s" s="2">
-        <v>329</v>
+        <v>703</v>
       </c>
       <c r="AR139" t="s" s="2">
         <v>85</v>
@@ -21038,10 +21018,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>815</v>
+        <v>704</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21061,23 +21041,19 @@
         <v>85</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>212</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>381</v>
+        <v>154</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>85</v>
       </c>
@@ -21125,7 +21101,7 @@
         <v>85</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>385</v>
+        <v>156</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>83</v>
@@ -21137,7 +21113,7 @@
         <v>85</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>85</v>
@@ -21155,10 +21131,10 @@
         <v>85</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>387</v>
+        <v>158</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>85</v>
@@ -21172,21 +21148,21 @@
         <v>816</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>85</v>
@@ -21195,20 +21171,18 @@
         <v>85</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>723</v>
+        <v>214</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>724</v>
+        <v>215</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>85</v>
       </c>
@@ -21232,13 +21206,13 @@
         <v>85</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>566</v>
+        <v>85</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>85</v>
@@ -21256,19 +21230,19 @@
         <v>85</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>722</v>
+        <v>162</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>726</v>
+        <v>85</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>85</v>
@@ -21286,10 +21260,10 @@
         <v>85</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>570</v>
+        <v>158</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>85</v>
@@ -21303,11 +21277,11 @@
         <v>817</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>728</v>
+        <v>706</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>572</v>
+        <v>641</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -21320,25 +21294,25 @@
         <v>85</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>573</v>
+        <v>642</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>575</v>
+        <v>199</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>576</v>
+        <v>200</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>85</v>
@@ -21363,13 +21337,13 @@
         <v>85</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>578</v>
+        <v>85</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>85</v>
@@ -21387,7 +21361,7 @@
         <v>85</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>728</v>
+        <v>644</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>83</v>
@@ -21399,7 +21373,7 @@
         <v>85</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>85</v>
@@ -21414,19 +21388,19 @@
         <v>85</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>579</v>
+        <v>85</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>581</v>
+        <v>138</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS142" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -21434,7 +21408,7 @@
         <v>818</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21442,34 +21416,34 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>730</v>
+        <v>708</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>634</v>
+        <v>710</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>635</v>
+        <v>711</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>85</v>
@@ -21479,7 +21453,7 @@
         <v>85</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>85</v>
+        <v>802</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>85</v>
@@ -21494,13 +21468,13 @@
         <v>85</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>85</v>
@@ -21518,13 +21492,13 @@
         <v>85</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>85</v>
@@ -21533,7 +21507,7 @@
         <v>107</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>85</v>
+        <v>819</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>85</v>
@@ -21545,16 +21519,16 @@
         <v>85</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>85</v>
+        <v>712</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>637</v>
+        <v>398</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>638</v>
+        <v>399</v>
       </c>
       <c r="AR143" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AS143" t="s" s="2">
         <v>85</v>
@@ -21562,14 +21536,12 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>820</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>85</v>
       </c>
@@ -21590,19 +21562,19 @@
         <v>96</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>631</v>
+        <v>491</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>700</v>
+        <v>495</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>85</v>
@@ -21627,43 +21599,41 @@
         <v>85</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>85</v>
+        <v>496</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>702</v>
+        <v>107</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>85</v>
@@ -21678,19 +21648,19 @@
         <v>85</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>703</v>
+        <v>500</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>704</v>
+        <v>501</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS144" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
     </row>
     <row r="145" hidden="true">
@@ -21698,9 +21668,11 @@
         <v>821</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>806</v>
+      </c>
       <c r="D145" t="s" s="2">
         <v>85</v>
       </c>
@@ -21712,25 +21684,29 @@
         <v>95</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>154</v>
+        <v>714</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
+        <v>715</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>85</v>
       </c>
@@ -21754,13 +21730,13 @@
         <v>85</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>85</v>
+        <v>822</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>85</v>
+        <v>823</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>85</v>
@@ -21778,7 +21754,7 @@
         <v>85</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>156</v>
+        <v>713</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>83</v>
@@ -21787,59 +21763,59 @@
         <v>95</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>85</v>
+        <v>824</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>158</v>
+        <v>501</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS145" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>85</v>
@@ -21848,18 +21824,20 @@
         <v>85</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>214</v>
+        <v>720</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>215</v>
+        <v>721</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>85</v>
       </c>
@@ -21883,13 +21861,13 @@
         <v>85</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>85</v>
@@ -21907,19 +21885,19 @@
         <v>85</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>162</v>
+        <v>719</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>85</v>
+        <v>723</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>85</v>
@@ -21937,10 +21915,10 @@
         <v>85</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>158</v>
+        <v>569</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>85</v>
@@ -21951,14 +21929,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>642</v>
+        <v>571</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -21971,25 +21949,25 @@
         <v>85</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>643</v>
+        <v>572</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>199</v>
+        <v>574</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>200</v>
+        <v>575</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>85</v>
@@ -22014,13 +21992,13 @@
         <v>85</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>85</v>
+        <v>577</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>85</v>
@@ -22038,7 +22016,7 @@
         <v>85</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>645</v>
+        <v>724</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>83</v>
@@ -22050,7 +22028,7 @@
         <v>85</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>85</v>
@@ -22065,27 +22043,27 @@
         <v>85</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>85</v>
+        <v>578</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>85</v>
+        <v>579</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>138</v>
+        <v>580</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS147" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22093,34 +22071,34 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>711</v>
+        <v>633</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>712</v>
+        <v>634</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>85</v>
@@ -22130,7 +22108,7 @@
         <v>85</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>802</v>
+        <v>85</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>85</v>
@@ -22145,13 +22123,13 @@
         <v>85</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>395</v>
+        <v>85</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>85</v>
@@ -22169,13 +22147,13 @@
         <v>85</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>85</v>
@@ -22184,7 +22162,7 @@
         <v>107</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>825</v>
+        <v>85</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>85</v>
@@ -22196,1196 +22174,23 @@
         <v>85</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>713</v>
+        <v>85</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>398</v>
+        <v>636</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>399</v>
+        <v>637</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AS148" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AC149" s="2"/>
-      <c r="AD149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AP149" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AQ149" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AR149" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS149" t="s" s="2">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="D150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AP150" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AQ150" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AR150" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS150" t="s" s="2">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ151" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AR151" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS151" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O152" s="2"/>
-      <c r="P152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ152" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AR152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS152" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP153" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AQ153" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AR153" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS153" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="P154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP154" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AQ154" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AR154" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS154" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP155" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AQ155" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AR155" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS155" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="P156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AP156" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AQ156" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AR156" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS156" t="s" s="2">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="P157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP157" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AQ157" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AR157" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS157" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS157">
+  <autoFilter ref="A1:AS148">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -23395,7 +22200,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI156">
+  <conditionalFormatting sqref="A2:AI147">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
